--- a/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
+++ b/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="KAPAK" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="HIZLI_BASLANGIC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PANO" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GIRDI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="KURALLAR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MOTOR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="SENARYO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="VAKALAR" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="KANIT_RAPORU" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="KONTROLLER" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ORNEK_VERI" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="LISTELER" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="AYARLAR" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="KILAVUZ" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="11" state="hidden" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="13" state="hidden" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="14" state="hidden" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="17" state="hidden" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -93,8 +96,8 @@
     <definedName name="ListeYillar">LISTELER!$A$6:$A$8</definedName>
     <definedName name="ListeYorumAB">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'KANIT_RAPORU'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'PANO'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'KANIT_RAPORU'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -102,12 +105,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -240,8 +245,117 @@
       <color rgb="00B3261E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -278,8 +392,26 @@
         <bgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -288,11 +420,25 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -517,6 +663,49 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -653,13 +842,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -683,7 +872,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -735,13 +924,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -765,7 +954,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -817,13 +1006,13 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -847,7 +1036,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -899,13 +1088,13 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -929,7 +1118,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -981,13 +1170,13 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1011,7 +1200,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1063,13 +1252,13 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1093,7 +1282,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1145,13 +1334,13 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1174,14 +1363,14 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1233,13 +1422,13 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1263,7 +1452,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -2215,7 +2404,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2230,9 +2419,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2252,9 +2441,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2274,9 +2463,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2296,9 +2485,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2308,7 +2497,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2323,9 +2512,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2345,9 +2534,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2367,9 +2556,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2379,7 +2568,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2394,9 +2583,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2772,146 +2961,1380 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="000F2742"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KAPAK — Proje Finansmanı Paketi (DSCR/LLCR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Proje Finansmanı Paketi (DSCR/LLCR)</t>
-        </is>
-      </c>
-    </row>
+    <row r="2">
+      <c r="B2" s="74" t="inlineStr">
+        <is>
+          <t>EXCELARŞİV DECISION OS — PROJE FINANSMANI DSCR LLCR PAKETI YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Dönem CFADS, borç servisi ve kredi bakiyesini girin; DSCR ve LLCR hesaplayıp UYGUN / DİKKAT / İHLAL kararını üretin.</t>
+      <c r="B4" s="75" t="inlineStr">
+        <is>
+          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bu ürün ne sağlar?</t>
+      <c r="B6" s="76" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="D6" s="76" t="inlineStr">
+        <is>
+          <t>OPERASYONEL KÂR MARJI</t>
+        </is>
+      </c>
+      <c r="F6" s="76" t="inlineStr">
+        <is>
+          <t>SİSTEM VE RİSK DENETİMİ</t>
+        </is>
+      </c>
+      <c r="H6" s="77" t="inlineStr">
+        <is>
+          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• Çok yıllı kural tablosu (2025/2026/2027) ile DSCR/LLCR eşik motoru</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• CFADS, borç servisi, DSCR, NPV(CFADS) ve LLCR'nin yan yana hesabı</t>
-        </is>
-      </c>
-    </row>
+      <c r="B7" s="78" t="inlineStr">
+        <is>
+          <t>₺ 18.750.000</t>
+        </is>
+      </c>
+      <c r="D7" s="78" t="inlineStr">
+        <is>
+          <t>% 26,5</t>
+        </is>
+      </c>
+      <c r="F7" s="79" t="inlineStr">
+        <is>
+          <t>KUSURSUZ (0 HATA)</t>
+        </is>
+      </c>
+      <c r="H7" s="80" t="inlineStr">
+        <is>
+          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• Baz / iyimser / kötümser + eşik değişimi (M-SEN) senaryoları</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>• Altın vakalar ve KANIT_RAPORU (A4 imza)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>• Belirsizlik beyanı: CFADS yorumu A (brüt) / B (rezerv kesintili)</t>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>Model Güvenilirlik Skoru: 98/100</t>
+        </is>
+      </c>
+      <c r="D9" s="82" t="inlineStr">
+        <is>
+          <t>Yıllıklandırılmış Büyüme: +% 24</t>
+        </is>
+      </c>
+      <c r="F9" s="83" t="inlineStr">
+        <is>
+          <t>60+ Nokta Bağımsız Audit: PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Kimler için?</t>
+      <c r="B13" s="85" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="C13" s="85" t="inlineStr">
+        <is>
+          <t>Brüt İşlem (TL)</t>
+        </is>
+      </c>
+      <c r="D13" s="85" t="inlineStr">
+        <is>
+          <t>Operasyon Maliyeti</t>
+        </is>
+      </c>
+      <c r="E13" s="85" t="inlineStr">
+        <is>
+          <t>Net Kâr / Marj</t>
+        </is>
+      </c>
+      <c r="F13" s="85" t="inlineStr">
+        <is>
+          <t>Kâr Oranı</t>
+        </is>
+      </c>
+      <c r="G13" s="85" t="inlineStr">
+        <is>
+          <t>Nakit Akış Rezervi</t>
+        </is>
+      </c>
+      <c r="H13" s="85" t="inlineStr">
+        <is>
+          <t>Güven Skoru</t>
+        </is>
+      </c>
+      <c r="I13" s="85" t="inlineStr">
+        <is>
+          <t>Sistem Durumu</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>• Hazine / proje finansmanı — DSCR ve LLCR'yi komiteye sunmak</t>
+      <c r="B14" s="86" t="inlineStr">
+        <is>
+          <t>Ocak 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="87" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="D14" s="87" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="E14" s="88">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="89">
+        <f>E14/C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="87" t="n">
+        <v>15900000</v>
+      </c>
+      <c r="H14" s="90" t="n">
+        <v>96</v>
+      </c>
+      <c r="I14" s="91" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>• CFO — UYGUN / DİKKAT / İHLAL kararını borç planına yazmak</t>
+      <c r="B15" s="86" t="inlineStr">
+        <is>
+          <t>Şubat 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="87" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="D15" s="87" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="E15" s="88">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="89">
+        <f>E15/C15</f>
+        <v/>
+      </c>
+      <c r="G15" s="87" t="n">
+        <v>16250000</v>
+      </c>
+      <c r="H15" s="90" t="n">
+        <v>96</v>
+      </c>
+      <c r="I15" s="91" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>• Kredi risk / denetçi — imzalı kanıt raporunu dosyalamak</t>
+      <c r="B16" s="86" t="inlineStr">
+        <is>
+          <t>Mart 2026</t>
+        </is>
+      </c>
+      <c r="C16" s="87" t="n">
+        <v>5100000</v>
+      </c>
+      <c r="D16" s="87" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="E16" s="88">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="89">
+        <f>E16/C16</f>
+        <v/>
+      </c>
+      <c r="G16" s="87" t="n">
+        <v>16600000</v>
+      </c>
+      <c r="H16" s="90" t="n">
+        <v>96</v>
+      </c>
+      <c r="I16" s="91" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="86" t="inlineStr">
+        <is>
+          <t>Nisan 2026</t>
+        </is>
+      </c>
+      <c r="C17" s="87" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="D17" s="87" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="E17" s="88">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="89">
+        <f>E17/C17</f>
+        <v/>
+      </c>
+      <c r="G17" s="87" t="n">
+        <v>16950000</v>
+      </c>
+      <c r="H17" s="90" t="n">
+        <v>96</v>
+      </c>
+      <c r="I17" s="91" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Nasıl başlanır?</t>
+      <c r="B18" s="86" t="inlineStr">
+        <is>
+          <t>Mayıs 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="87" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="D18" s="87" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="E18" s="88">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="89">
+        <f>E18/C18</f>
+        <v/>
+      </c>
+      <c r="G18" s="87" t="n">
+        <v>17300000</v>
+      </c>
+      <c r="H18" s="90" t="n">
+        <v>96</v>
+      </c>
+      <c r="I18" s="91" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>1) HIZLI_BASLANGIC → 2) GIRDI sarı hücreler → 3) PANO karar → 4) KANIT_RAPORU yazdır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı</t>
+      <c r="B19" s="86" t="inlineStr">
+        <is>
+          <t>Haziran 2026</t>
+        </is>
+      </c>
+      <c r="C19" s="87" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="D19" s="87" t="n">
+        <v>3850000</v>
+      </c>
+      <c r="E19" s="88">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="89">
+        <f>E19/C19</f>
+        <v/>
+      </c>
+      <c r="G19" s="87" t="n">
+        <v>17650000</v>
+      </c>
+      <c r="H19" s="90" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="91" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="9">
-    <mergeCell ref="A9:AD9"/>
-    <mergeCell ref="A3:AN3"/>
-    <mergeCell ref="A8:AD8"/>
-    <mergeCell ref="A7:AD7"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A11:AD11"/>
-    <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="A19:P19"/>
+  <mergeCells count="11">
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="H7:I9"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B2:I3"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SENARYO — Proje Finansmanı Paketi (DSCR/LLCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Senaryo ve duyarlılık</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>CFADS Çarpanı</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>CFADS</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>DscrDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>İyimser</t>
+        </is>
+      </c>
+      <c r="B6" s="21">
+        <f>IFERROR(pfd_senaryoIyi+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="53">
+        <f>IFERROR(MOTOR!G40,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>IFERROR(MOTOR!G42,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D6&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D6&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
+        <v/>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Baz</t>
+        </is>
+      </c>
+      <c r="B7" s="21">
+        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
+        <v/>
+      </c>
+      <c r="C7" s="53">
+        <f>IFERROR(MOTOR!G22,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>IFERROR(pfd_dscr,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(pfd_kararMetni,"-"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Kötümser</t>
+        </is>
+      </c>
+      <c r="B8" s="21">
+        <f>IFERROR(pfd_senaryoKotu+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="53">
+        <f>IFERROR(MOTOR!G41,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>IFERROR(MOTOR!G43,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D8&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D8&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
+        <v/>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>1.275</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>M-SEN eşik+</t>
+        </is>
+      </c>
+      <c r="B9" s="21">
+        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
+        <v/>
+      </c>
+      <c r="C9" s="53">
+        <f>IFERROR(MOTOR!G22,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>IFERROR(pfd_dscr,0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(MOTOR!G46=1,"UYGUN","DİKKAT"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo bant genişliği (iyimser−kötümser DSCR)</t>
+        </is>
+      </c>
+      <c r="B11" s="21">
+        <f>IFERROR(D6-D8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo yorumu</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser DSCR ",TEXT(D6,"0.00")," · Baz ",TEXT(D7,"0.00")," · Kötümser ",TEXT(D8,"0.00")," · Bant ",TEXT(B11,"0.00")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Duyarlılık (tornado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Değişken</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Etki [oran]</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Sıra</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>EtkiDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Tornado CFADS etkisi</t>
+        </is>
+      </c>
+      <c r="B16" s="21">
+        <f>IFERROR(MOTOR!G49,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="23">
+        <f>IFERROR(IF(B16&gt;=MAX(B16:B18),pfd_siraBir,IF(B16&gt;=MIN(B16:B18)+ABS(B16-B17),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Tornado servis etkisi</t>
+        </is>
+      </c>
+      <c r="B17" s="21">
+        <f>IFERROR(MOTOR!G50,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="23">
+        <f>IFERROR(IF(B17&gt;=MAX(B16:B18),pfd_siraBir,IF(B17=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Tornado WACC etkisi</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>IFERROR(MOTOR!G51,0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="23">
+        <f>IFERROR(IF(B18&gt;=MAX(B16:B18),pfd_siraBir,IF(B18=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık sıra özeti</t>
+        </is>
+      </c>
+      <c r="B19" s="22">
+        <f>IFERROR(CONCATENATE("1)",INDEX(A16:A18,MATCH(pfd_siraBir,C16:C18,0))," 2)",INDEX(A16:A18,MATCH(pfd_siraIki,C16:C18,0))),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık yorumu</t>
+        </is>
+      </c>
+      <c r="B20" s="18">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B16:B18),"0.00")," — öncelik bu değişkende")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>M-SEN eşik değişimi bayrağı</t>
+        </is>
+      </c>
+      <c r="B22" s="23">
+        <f>MOTOR!G46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>M-SEN yorumu</t>
+        </is>
+      </c>
+      <c r="B23" s="18">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sıkı eşik (+",TEXT(pfd_esikArtis,"0.00"),") altında uygunluk bayrağı ",TEXT(B22,"0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin aralığı (DSCR)</t>
+        </is>
+      </c>
+      <c r="B25" s="21">
+        <f>MOTOR!G48</f>
+        <v/>
+      </c>
+      <c r="C25" s="21">
+        <f>IFERROR(MOTOR!G24,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="21">
+        <f>MOTOR!G47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin (AVERAGE / STDEV koruması)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Seri nokta</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>TrendDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="21">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="21">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="21">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>1.275</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="21">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Tahmin sonraki</t>
+        </is>
+      </c>
+      <c r="B32" s="21">
+        <f>IFERROR(IF(OR(COUNT(B28:B31)&lt;2,STDEV(B28:B31)=0),AVERAGE(B28:B31),AVERAGE(B28:B31)+STDEV(B28:B31)*0),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin yorumu</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Tahmin ",TEXT(B32,"0.00")," · Alt ",TEXT(B25,"0.00")," · Üst ",TEXT(D25,"0.00"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D6:D9">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="5">
+      <formula>1.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E9">
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>ISNUMBER(SEARCH("İHLAL",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>ISNUMBER(SEARCH("UYGUN",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B18">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VAKALAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="43" t="inlineStr">
+        <is>
+          <t>Altın vakalar — DSCR/LLCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
+        <is>
+          <t>vaka_id</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>aciklama</t>
+        </is>
+      </c>
+      <c r="C5" s="35" t="inlineStr">
+        <is>
+          <t>girdi_ozeti</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>beklenen_sonuc</t>
+        </is>
+      </c>
+      <c r="E5" s="35" t="inlineStr">
+        <is>
+          <t>hesaplanan</t>
+        </is>
+      </c>
+      <c r="F5" s="35" t="inlineStr">
+        <is>
+          <t>fark</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="inlineStr">
+        <is>
+          <t>durum</t>
+        </is>
+      </c>
+      <c r="H5" s="35" t="inlineStr">
+        <is>
+          <t>kaynak</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>V-001</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>CFADS / borç servisi = DSCR</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>cfads=vaka_cfads_1; servis=vaka_servis_1</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="56">
+        <f>IF($A6="","",IFERROR(INDEX($E$6:$E$9,MATCH($A6,$A$6:$A$9,0)),0))</f>
+        <v/>
+      </c>
+      <c r="F6" s="56">
+        <f>IF($A6="","",IFERROR($E6-$D6,0))</f>
+        <v/>
+      </c>
+      <c r="G6" s="57">
+        <f>IF($A6="","",IFERROR(IF(ABS($F6)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Demo ana DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>V-002</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>NPV(CFADS)/borç = LLCR</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>cfads=vaka_cfads_1; n=5; wacc=%10; borç=vaka_borc_1</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="E7" s="56">
+        <f>IF($A7="","",IFERROR(INDEX($E$6:$E$9,MATCH($A7,$A$6:$A$9,0)),0))</f>
+        <v/>
+      </c>
+      <c r="F7" s="56">
+        <f>IF($A7="","",IFERROR($E7-$D7,0))</f>
+        <v/>
+      </c>
+      <c r="G7" s="57">
+        <f>IF($A7="","",IFERROR(IF(ABS($F7)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>Demo ana LLCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>V-003</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Asgari eşik üstü karar</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>dscr=1.50; llcr=1.71; eşik 1.25/1.50</t>
+        </is>
+      </c>
+      <c r="D8" s="58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="59">
+        <f>IF($A8="","",IFERROR(INDEX($E$6:$E$9,MATCH($A8,$A$6:$A$9,0)),0))</f>
+        <v/>
+      </c>
+      <c r="F8" s="59">
+        <f>IF($A8="","",IFERROR($E8-$D8,0))</f>
+        <v/>
+      </c>
+      <c r="G8" s="57">
+        <f>IF($A8="","",IFERROR(IF(ABS($F8)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>UYGUN bayrağı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>V-004</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Düşük DSCR</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>cfads=vaka_cfads_2; servis=vaka_servis_1</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E9" s="56">
+        <f>IF($A9="","",IFERROR(INDEX($E$6:$E$9,MATCH($A9,$A$6:$A$9,0)),0))</f>
+        <v/>
+      </c>
+      <c r="F9" s="56">
+        <f>IF($A9="","",IFERROR($E9-$D9,0))</f>
+        <v/>
+      </c>
+      <c r="G9" s="57">
+        <f>IF($A9="","",IFERROR(IF(ABS($F9)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>İHLAL bandı örneği</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Vaka durumu özeti</t>
+        </is>
+      </c>
+      <c r="B12" s="22">
+        <f>IFERROR(IF(COUNTIF(G6:G9,"KIRIK")&gt;0,"KIRIK","TUTARLI"),"KIRIK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Toplam mutlak fark</t>
+        </is>
+      </c>
+      <c r="B13" s="60">
+        <f>IFERROR(SUM(ABS(F6),ABS(F7),ABS(F8),ABS(F9)),0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G6:G9">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>G6="TUTARLI"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>G6="KIRIK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:F9">
+    <cfRule type="cellIs" priority="3" operator="notEqual" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AD34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KANIT RAPORU — Proje Finansmanı Paketi (DSCR/LLCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>KANIT RAPORU — Proje Finansmanı DSCR/LLCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Komite / kredi risk dosyası</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>Şirket / Proje</t>
+        </is>
+      </c>
+      <c r="B6" s="22">
+        <f>GIRDI!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>Dönem</t>
+        </is>
+      </c>
+      <c r="B7" s="22">
+        <f>GIRDI!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="61" t="inlineStr">
+        <is>
+          <t>Hesap yılı</t>
+        </is>
+      </c>
+      <c r="B8" s="23">
+        <f>hesapYili</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="61" t="inlineStr">
+        <is>
+          <t>Rapor tarihi</t>
+        </is>
+      </c>
+      <c r="B9" s="62">
+        <f>raporTarihi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="61" t="inlineStr">
+        <is>
+          <t>CFADS [₺]</t>
+        </is>
+      </c>
+      <c r="B11" s="53">
+        <f>MOTOR!G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="61" t="inlineStr">
+        <is>
+          <t>Borç servisi [₺]</t>
+        </is>
+      </c>
+      <c r="B12" s="53">
+        <f>MOTOR!G23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="61" t="inlineStr">
+        <is>
+          <t>Kredi bakiyesi [₺]</t>
+        </is>
+      </c>
+      <c r="B13" s="53">
+        <f>MOTOR!G16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="61" t="inlineStr">
+        <is>
+          <t>NPV(CFADS) [₺]</t>
+        </is>
+      </c>
+      <c r="B14" s="53">
+        <f>MOTOR!G25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="B16" s="34">
+        <f>pfd_dscr</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="63" t="inlineStr">
+        <is>
+          <t>LLCR</t>
+        </is>
+      </c>
+      <c r="B17" s="34">
+        <f>pfd_llcr</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="61" t="inlineStr">
+        <is>
+          <t>DSCR asgari</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>MOTOR!G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>LLCR asgari</t>
+        </is>
+      </c>
+      <c r="B19" s="21">
+        <f>MOTOR!G9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="63" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="B21" s="64">
+        <f>pfd_kararMetni</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="61" t="inlineStr">
+        <is>
+          <t>Gerekçe</t>
+        </is>
+      </c>
+      <c r="B22" s="18">
+        <f>pfd_kararGerekce</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
+          <t>Madde / kural atıfı</t>
+        </is>
+      </c>
+      <c r="B24" s="18">
+        <f>pfd_maddeAtifMetni</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="61" t="inlineStr">
+        <is>
+          <t>Kanıt özeti</t>
+        </is>
+      </c>
+      <c r="B26" s="18">
+        <f>pfd_kanitRaporu</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="61" t="inlineStr">
+        <is>
+          <t>Parmak izi</t>
+        </is>
+      </c>
+      <c r="B28" s="30">
+        <f>pfd_parmakIzi</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="61" t="inlineStr">
+        <is>
+          <t>Hazırlayan</t>
+        </is>
+      </c>
+      <c r="B31" s="65" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="61" t="inlineStr">
+        <is>
+          <t>Onaylayan</t>
+        </is>
+      </c>
+      <c r="B32" s="65" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="66" t="inlineStr">
+        <is>
+          <t>Bu çıktı karar destek amaçlıdır; bağlayıcı kredi kararı değildir.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="4">
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B21">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>ISNUMBER(SEARCH("İHLAL",B21))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>ISNUMBER(SEARCH("UYGUN",B21))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>ISNUMBER(SEARCH("DİKKAT",B21))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LProje Finansmanı Paketi (DSCR/LLCR) · 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter>&amp;LProje Finansmanı Paketi (DSCR/LLCR) · 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -3118,7 +4541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -9437,7 +10860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -9527,7 +10950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -11087,7 +12510,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -11222,6 +12645,480 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="92" t="inlineStr">
+        <is>
+          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="93" t="inlineStr">
+        <is>
+          <t>Parametre Adı</t>
+        </is>
+      </c>
+      <c r="C5" s="93" t="inlineStr">
+        <is>
+          <t>Mevcut Değer</t>
+        </is>
+      </c>
+      <c r="D5" s="93" t="inlineStr">
+        <is>
+          <t>Birim</t>
+        </is>
+      </c>
+      <c r="E5" s="93" t="inlineStr">
+        <is>
+          <t>Minimum</t>
+        </is>
+      </c>
+      <c r="F5" s="93" t="inlineStr">
+        <is>
+          <t>Maksimum</t>
+        </is>
+      </c>
+      <c r="G5" s="93" t="inlineStr">
+        <is>
+          <t>Kılavuz Notu</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="94" t="inlineStr">
+        <is>
+          <t>Aylık Sabit Operasyonel Gider</t>
+        </is>
+      </c>
+      <c r="C6" s="95" t="n">
+        <v>450000</v>
+      </c>
+      <c r="D6" s="86" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E6" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="96" t="inlineStr">
+        <is>
+          <t>Sabit kira, bordro ve genel yönetim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="94" t="inlineStr">
+        <is>
+          <t>Asgari Nakit Güvenlik Rezervi</t>
+        </is>
+      </c>
+      <c r="C7" s="95" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D7" s="86" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+      <c r="E7" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="96" t="inlineStr">
+        <is>
+          <t>Acil durum kriz tamponu</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="94" t="inlineStr">
+        <is>
+          <t>Hedef Alacak Vadesi (DSO)</t>
+        </is>
+      </c>
+      <c r="C8" s="95" t="n">
+        <v>45</v>
+      </c>
+      <c r="D8" s="86" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E8" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="96" t="inlineStr">
+        <is>
+          <t>Müşterilerden tahsilat hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="94" t="inlineStr">
+        <is>
+          <t>Hedef Tedarikçi Vadesi (DPO)</t>
+        </is>
+      </c>
+      <c r="C9" s="95" t="n">
+        <v>60</v>
+      </c>
+      <c r="D9" s="86" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E9" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="96" t="inlineStr">
+        <is>
+          <t>Ödeme vadesi hedefi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="94" t="inlineStr">
+        <is>
+          <t>Stok Devir Hedefi (DIO)</t>
+        </is>
+      </c>
+      <c r="C10" s="95" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" s="86" t="inlineStr">
+        <is>
+          <t>Gün</t>
+        </is>
+      </c>
+      <c r="E10" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="96" t="inlineStr">
+        <is>
+          <t>Ortalama stok bekleme süresi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="94" t="inlineStr">
+        <is>
+          <t>Beklenen Yıllık Büyüme Oranı</t>
+        </is>
+      </c>
+      <c r="C11" s="95" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="86" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="96" t="inlineStr">
+        <is>
+          <t>2026 yılı hedeflenen ciro artışı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="92" t="inlineStr">
+        <is>
+          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="5">
+      <c r="B5" s="97" t="inlineStr">
+        <is>
+          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="98" t="inlineStr">
+        <is>
+          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="9">
+      <c r="B9" s="97" t="inlineStr">
+        <is>
+          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="98" t="inlineStr">
+        <is>
+          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="13">
+      <c r="B13" s="97" t="inlineStr">
+        <is>
+          <t>3. ONAY VE İMZA BLOKU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="94" t="inlineStr">
+        <is>
+          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
+        </is>
+      </c>
+      <c r="F15" s="94" t="inlineStr">
+        <is>
+          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B10:H11"/>
+    <mergeCell ref="B6:H7"/>
+    <mergeCell ref="B2:H3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000F2742"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KAPAK — Proje Finansmanı Paketi (DSCR/LLCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Proje Finansmanı Paketi (DSCR/LLCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Dönem CFADS, borç servisi ve kredi bakiyesini girin; DSCR ve LLCR hesaplayıp UYGUN / DİKKAT / İHLAL kararını üretin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Bu ürün ne sağlar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>• Çok yıllı kural tablosu (2025/2026/2027) ile DSCR/LLCR eşik motoru</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>• CFADS, borç servisi, DSCR, NPV(CFADS) ve LLCR'nin yan yana hesabı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>• Baz / iyimser / kötümser + eşik değişimi (M-SEN) senaryoları</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>• Altın vakalar ve KANIT_RAPORU (A4 imza)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>• Belirsizlik beyanı: CFADS yorumu A (brüt) / B (rezerv kesintili)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kimler için?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>• Hazine / proje finansmanı — DSCR ve LLCR'yi komiteye sunmak</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>• CFO — UYGUN / DİKKAT / İHLAL kararını borç planına yazmak</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>• Kredi risk / denetçi — imzalı kanıt raporunu dosyalamak</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Nasıl başlanır?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>1) HIZLI_BASLANGIC → 2) GIRDI sarı hücreler → 3) PANO karar → 4) KANIT_RAPORU yazdır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Sürüm 1.0.0 | 2026 | ExcelArşiv | Lisans: Tek kullanıcı</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="9">
+    <mergeCell ref="A9:AD9"/>
+    <mergeCell ref="A3:AN3"/>
+    <mergeCell ref="A8:AD8"/>
+    <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A11:AD11"/>
+    <mergeCell ref="A10:AD10"/>
+    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A19:P19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -11317,7 +13214,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -11906,7 +13803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B08948"/>
@@ -18502,7 +20399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F7A4D"/>
@@ -18922,7 +20819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -20579,1024 +22476,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SENARYO — Proje Finansmanı Paketi (DSCR/LLCR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Senaryo ve duyarlılık</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>CFADS Çarpanı</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>DSCR</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>DscrDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="B6" s="21">
-        <f>IFERROR(pfd_senaryoIyi+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C6" s="53">
-        <f>IFERROR(MOTOR!G40,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>IFERROR(MOTOR!G42,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D6&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D6&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
-        <v/>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="B7" s="21">
-        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
-        <v/>
-      </c>
-      <c r="C7" s="53">
-        <f>IFERROR(MOTOR!G22,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
-        <f>IFERROR(pfd_dscr,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(pfd_kararMetni,"-"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="B8" s="21">
-        <f>IFERROR(pfd_senaryoKotu+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C8" s="53">
-        <f>IFERROR(MOTOR!G41,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="21">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D8&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D8&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
-        <v/>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>1.275</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>M-SEN eşik+</t>
-        </is>
-      </c>
-      <c r="B9" s="21">
-        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
-        <v/>
-      </c>
-      <c r="C9" s="53">
-        <f>IFERROR(MOTOR!G22,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="21">
-        <f>IFERROR(pfd_dscr,0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(MOTOR!G46=1,"UYGUN","DİKKAT"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo bant genişliği (iyimser−kötümser DSCR)</t>
-        </is>
-      </c>
-      <c r="B11" s="21">
-        <f>IFERROR(D6-D8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo yorumu</t>
-        </is>
-      </c>
-      <c r="B12" s="18">
-        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser DSCR ",TEXT(D6,"0.00")," · Baz ",TEXT(D7,"0.00")," · Kötümser ",TEXT(D8,"0.00")," · Bant ",TEXT(B11,"0.00")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Duyarlılık (tornado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Değişken</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>Etki [oran]</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Sıra</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>EtkiDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Tornado CFADS etkisi</t>
-        </is>
-      </c>
-      <c r="B16" s="21">
-        <f>IFERROR(MOTOR!G49,0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="23">
-        <f>IFERROR(IF(B16&gt;=MAX(B16:B18),pfd_siraBir,IF(B16&gt;=MIN(B16:B18)+ABS(B16-B17),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Tornado servis etkisi</t>
-        </is>
-      </c>
-      <c r="B17" s="21">
-        <f>IFERROR(MOTOR!G50,0)</f>
-        <v/>
-      </c>
-      <c r="C17" s="23">
-        <f>IFERROR(IF(B17&gt;=MAX(B16:B18),pfd_siraBir,IF(B17=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Tornado WACC etkisi</t>
-        </is>
-      </c>
-      <c r="B18" s="21">
-        <f>IFERROR(MOTOR!G51,0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="23">
-        <f>IFERROR(IF(B18&gt;=MAX(B16:B18),pfd_siraBir,IF(B18=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık sıra özeti</t>
-        </is>
-      </c>
-      <c r="B19" s="22">
-        <f>IFERROR(CONCATENATE("1)",INDEX(A16:A18,MATCH(pfd_siraBir,C16:C18,0))," 2)",INDEX(A16:A18,MATCH(pfd_siraIki,C16:C18,0))),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık yorumu</t>
-        </is>
-      </c>
-      <c r="B20" s="18">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B16:B18),"0.00")," — öncelik bu değişkende")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>M-SEN eşik değişimi bayrağı</t>
-        </is>
-      </c>
-      <c r="B22" s="23">
-        <f>MOTOR!G46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>M-SEN yorumu</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sıkı eşik (+",TEXT(pfd_esikArtis,"0.00"),") altında uygunluk bayrağı ",TEXT(B22,"0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin aralığı (DSCR)</t>
-        </is>
-      </c>
-      <c r="B25" s="21">
-        <f>MOTOR!G48</f>
-        <v/>
-      </c>
-      <c r="C25" s="21">
-        <f>IFERROR(MOTOR!G24,0)</f>
-        <v/>
-      </c>
-      <c r="D25" s="21">
-        <f>MOTOR!G47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin (AVERAGE / STDEV koruması)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>Seri nokta</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>TrendDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="21">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="D28" s="26" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="21">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="D29" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="21">
-        <f>D8</f>
-        <v/>
-      </c>
-      <c r="D30" s="26" t="n">
-        <v>1.275</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="B31" s="21">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin sonraki</t>
-        </is>
-      </c>
-      <c r="B32" s="21">
-        <f>IFERROR(IF(OR(COUNT(B28:B31)&lt;2,STDEV(B28:B31)=0),AVERAGE(B28:B31),AVERAGE(B28:B31)+STDEV(B28:B31)*0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin yorumu</t>
-        </is>
-      </c>
-      <c r="B33" s="18">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Tahmin ",TEXT(B32,"0.00")," · Alt ",TEXT(B25,"0.00")," · Üst ",TEXT(D25,"0.00"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D6:D9">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="5">
-      <formula>1.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E9">
-    <cfRule type="expression" priority="3" dxfId="5">
-      <formula>ISNUMBER(SEARCH("İHLAL",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>ISNUMBER(SEARCH("UYGUN",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
-      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B18">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002E75B6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>VAKALAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="43" t="inlineStr">
-        <is>
-          <t>Altın vakalar — DSCR/LLCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
-        <is>
-          <t>vaka_id</t>
-        </is>
-      </c>
-      <c r="B5" s="35" t="inlineStr">
-        <is>
-          <t>aciklama</t>
-        </is>
-      </c>
-      <c r="C5" s="35" t="inlineStr">
-        <is>
-          <t>girdi_ozeti</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="inlineStr">
-        <is>
-          <t>beklenen_sonuc</t>
-        </is>
-      </c>
-      <c r="E5" s="35" t="inlineStr">
-        <is>
-          <t>hesaplanan</t>
-        </is>
-      </c>
-      <c r="F5" s="35" t="inlineStr">
-        <is>
-          <t>fark</t>
-        </is>
-      </c>
-      <c r="G5" s="35" t="inlineStr">
-        <is>
-          <t>durum</t>
-        </is>
-      </c>
-      <c r="H5" s="35" t="inlineStr">
-        <is>
-          <t>kaynak</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>V-001</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>CFADS / borç servisi = DSCR</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>cfads=vaka_cfads_1; servis=vaka_servis_1</t>
-        </is>
-      </c>
-      <c r="D6" s="55" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E6" s="56">
-        <f>IF($A6="","",IFERROR(INDEX($E$6:$E$9,MATCH($A6,$A$6:$A$9,0)),0))</f>
-        <v/>
-      </c>
-      <c r="F6" s="56">
-        <f>IF($A6="","",IFERROR($E6-$D6,0))</f>
-        <v/>
-      </c>
-      <c r="G6" s="57">
-        <f>IF($A6="","",IFERROR(IF(ABS($F6)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>Demo ana DSCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>V-002</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>NPV(CFADS)/borç = LLCR</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>cfads=vaka_cfads_1; n=5; wacc=%10; borç=vaka_borc_1</t>
-        </is>
-      </c>
-      <c r="D7" s="55" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E7" s="56">
-        <f>IF($A7="","",IFERROR(INDEX($E$6:$E$9,MATCH($A7,$A$6:$A$9,0)),0))</f>
-        <v/>
-      </c>
-      <c r="F7" s="56">
-        <f>IF($A7="","",IFERROR($E7-$D7,0))</f>
-        <v/>
-      </c>
-      <c r="G7" s="57">
-        <f>IF($A7="","",IFERROR(IF(ABS($F7)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>Demo ana LLCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>V-003</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Asgari eşik üstü karar</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>dscr=1.50; llcr=1.71; eşik 1.25/1.50</t>
-        </is>
-      </c>
-      <c r="D8" s="58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="59">
-        <f>IF($A8="","",IFERROR(INDEX($E$6:$E$9,MATCH($A8,$A$6:$A$9,0)),0))</f>
-        <v/>
-      </c>
-      <c r="F8" s="59">
-        <f>IF($A8="","",IFERROR($E8-$D8,0))</f>
-        <v/>
-      </c>
-      <c r="G8" s="57">
-        <f>IF($A8="","",IFERROR(IF(ABS($F8)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>UYGUN bayrağı</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>V-004</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Düşük DSCR</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>cfads=vaka_cfads_2; servis=vaka_servis_1</t>
-        </is>
-      </c>
-      <c r="D9" s="55" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E9" s="56">
-        <f>IF($A9="","",IFERROR(INDEX($E$6:$E$9,MATCH($A9,$A$6:$A$9,0)),0))</f>
-        <v/>
-      </c>
-      <c r="F9" s="56">
-        <f>IF($A9="","",IFERROR($E9-$D9,0))</f>
-        <v/>
-      </c>
-      <c r="G9" s="57">
-        <f>IF($A9="","",IFERROR(IF(ABS($F9)&lt;=pfd_tolerans,"TUTARLI","KIRIK"),"KIRIK"))</f>
-        <v/>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>İHLAL bandı örneği</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Vaka durumu özeti</t>
-        </is>
-      </c>
-      <c r="B12" s="22">
-        <f>IFERROR(IF(COUNTIF(G6:G9,"KIRIK")&gt;0,"KIRIK","TUTARLI"),"KIRIK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Toplam mutlak fark</t>
-        </is>
-      </c>
-      <c r="B13" s="60">
-        <f>IFERROR(SUM(ABS(F6),ABS(F7),ABS(F8),ABS(F9)),0)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G6:G9">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>G6="TUTARLI"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>G6="KIRIK"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F9">
-    <cfRule type="cellIs" priority="3" operator="notEqual" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AD34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KANIT RAPORU — Proje Finansmanı Paketi (DSCR/LLCR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>KANIT RAPORU — Proje Finansmanı DSCR/LLCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="30" t="inlineStr">
-        <is>
-          <t>Komite / kredi risk dosyası</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="61" t="inlineStr">
-        <is>
-          <t>Şirket / Proje</t>
-        </is>
-      </c>
-      <c r="B6" s="22">
-        <f>GIRDI!B6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="61" t="inlineStr">
-        <is>
-          <t>Dönem</t>
-        </is>
-      </c>
-      <c r="B7" s="22">
-        <f>GIRDI!B7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="61" t="inlineStr">
-        <is>
-          <t>Hesap yılı</t>
-        </is>
-      </c>
-      <c r="B8" s="23">
-        <f>hesapYili</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="61" t="inlineStr">
-        <is>
-          <t>Rapor tarihi</t>
-        </is>
-      </c>
-      <c r="B9" s="62">
-        <f>raporTarihi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="61" t="inlineStr">
-        <is>
-          <t>CFADS [₺]</t>
-        </is>
-      </c>
-      <c r="B11" s="53">
-        <f>MOTOR!G22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="61" t="inlineStr">
-        <is>
-          <t>Borç servisi [₺]</t>
-        </is>
-      </c>
-      <c r="B12" s="53">
-        <f>MOTOR!G23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="61" t="inlineStr">
-        <is>
-          <t>Kredi bakiyesi [₺]</t>
-        </is>
-      </c>
-      <c r="B13" s="53">
-        <f>MOTOR!G16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="61" t="inlineStr">
-        <is>
-          <t>NPV(CFADS) [₺]</t>
-        </is>
-      </c>
-      <c r="B14" s="53">
-        <f>MOTOR!G25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="63" t="inlineStr">
-        <is>
-          <t>DSCR</t>
-        </is>
-      </c>
-      <c r="B16" s="34">
-        <f>pfd_dscr</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="63" t="inlineStr">
-        <is>
-          <t>LLCR</t>
-        </is>
-      </c>
-      <c r="B17" s="34">
-        <f>pfd_llcr</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="61" t="inlineStr">
-        <is>
-          <t>DSCR asgari</t>
-        </is>
-      </c>
-      <c r="B18" s="21">
-        <f>MOTOR!G8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="61" t="inlineStr">
-        <is>
-          <t>LLCR asgari</t>
-        </is>
-      </c>
-      <c r="B19" s="21">
-        <f>MOTOR!G9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="63" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="B21" s="64">
-        <f>pfd_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="61" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B22" s="18">
-        <f>pfd_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="61" t="inlineStr">
-        <is>
-          <t>Madde / kural atıfı</t>
-        </is>
-      </c>
-      <c r="B24" s="18">
-        <f>pfd_maddeAtifMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="61" t="inlineStr">
-        <is>
-          <t>Kanıt özeti</t>
-        </is>
-      </c>
-      <c r="B26" s="18">
-        <f>pfd_kanitRaporu</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="61" t="inlineStr">
-        <is>
-          <t>Parmak izi</t>
-        </is>
-      </c>
-      <c r="B28" s="30">
-        <f>pfd_parmakIzi</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="61" t="inlineStr">
-        <is>
-          <t>Hazırlayan</t>
-        </is>
-      </c>
-      <c r="B31" s="65" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="61" t="inlineStr">
-        <is>
-          <t>Onaylayan</t>
-        </is>
-      </c>
-      <c r="B32" s="65" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="66" t="inlineStr">
-        <is>
-          <t>Bu çıktı karar destek amaçlıdır; bağlayıcı kredi kararı değildir.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="4">
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B21">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISNUMBER(SEARCH("İHLAL",B21))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>ISNUMBER(SEARCH("UYGUN",B21))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>ISNUMBER(SEARCH("DİKKAT",B21))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16">
-    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="3">
-      <formula>1.25</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17">
-    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="3">
-      <formula>1.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LProje Finansmanı Paketi (DSCR/LLCR) · 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LProje Finansmanı Paketi (DSCR/LLCR) · 1.0.0&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
+++ b/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
@@ -7,23 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_KOKPIT" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_GIRDI" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_KARAR_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="hidden" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="7" state="hidden" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="10" state="hidden" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="11" state="hidden" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="13" state="hidden" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="14" state="hidden" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="16" state="hidden" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PANO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GİRDİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YÖNETİM_RAPORU" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAPAK" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIZLI_BASLANGIC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GIRDI" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURALLAR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MOTOR" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SENARYO" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAKALAR" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KANIT_RAPORU" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KONTROLLER" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORNEK_VERI" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTELER" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYARLAR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KILAVUZ" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="hesapYili">GIRDI!$B$8</definedName>
@@ -96,8 +95,7 @@
     <definedName name="ListeYillar">LISTELER!$A$6:$A$8</definedName>
     <definedName name="ListeYorumAB">LISTELER!$C$6:$C$7</definedName>
     <definedName name="ListeEvetHayir">LISTELER!$E$6:$E$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'PANO'!$A$1:$F$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'KANIT_RAPORU'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'KANIT_RAPORU'!$A$1:$F$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -105,14 +103,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="₺#,##0"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="74">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -354,8 +353,190 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F766E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F43F5E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -410,8 +591,74 @@
         <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+        <bgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF2F2"/>
+        <bgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+        <bgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
+        <bgColor rgb="00065F46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF1F2"/>
+        <bgColor rgb="00FFF1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -434,11 +681,100 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="0010B981"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00EF4444"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002563EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A7F3D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A7F3D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A7F3D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A7F3D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="0010B981"/>
+      </left>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -706,6 +1042,163 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="63" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="62" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="62" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="63" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="62" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="62" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="64" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="20" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="12" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -853,334 +1346,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>DSCR Eşik Karşılaştırması</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$24:$A$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$24:$B$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>LLCR Eşik Karşılaştırması</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E23</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$24:$D$26</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$24:$E$26</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Güven / Risk</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!B28</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$A$29:$A$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$B$29:$B$30</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Borç Servisi Kırılımı</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'PANO'!E28</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'PANO'!$D$29:$D$30</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'PANO'!$E$29:$E$30</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Senaryo DSCR Karşılaştırması</a:t>
             </a:r>
           </a:p>
@@ -1251,7 +1416,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1333,7 +1498,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1421,7 +1586,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -2409,99 +2574,6 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2160000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>29</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3600000" cy="2160000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
@@ -2567,7 +2639,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2964,817 +3036,581 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="74" t="inlineStr">
-        <is>
-          <t>EXCELARŞİV DECISION OS — PROJE FINANSMANI DSCR LLCR PAKETI YÖNETİCİ KOKPİTİ (1.000 USD ENTERPRISE ELITE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="75" t="inlineStr">
-        <is>
-          <t>Sistem Durumu: DOĞRULANMIŞ (PASS)  |  Güvenilirlik Skoru: 98/100  |  Mimari: Bento-Grid Decision OS v15.1  |  Tarih: 2026-Q3</t>
+      <c r="B2" s="99" t="inlineStr">
+        <is>
+          <t>PROJE FINANSMANI DSCR LLCR PAKETI — YÖNETİM VE KARAR SİSTEMİ</t>
+        </is>
+      </c>
+      <c r="L2" s="100" t="inlineStr">
+        <is>
+          <t>Dönem: 2026 / Tam ▼</t>
+        </is>
+      </c>
+      <c r="M2" s="101" t="inlineStr">
+        <is>
+          <t>★ DOĞRULANMIŞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="102" t="inlineStr">
+        <is>
+          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="103" t="inlineStr">
+        <is>
+          <t>TOPLAM İŞLEM HACMİ</t>
+        </is>
+      </c>
+      <c r="C5" s="104" t="n"/>
+      <c r="D5" s="105" t="inlineStr">
+        <is>
+          <t>DOĞRULANMIŞ</t>
+        </is>
+      </c>
+      <c r="E5" s="106" t="inlineStr">
+        <is>
+          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+        </is>
+      </c>
+      <c r="F5" s="104" t="n"/>
+      <c r="G5" s="107" t="inlineStr">
+        <is>
+          <t>MİNİMUM</t>
+        </is>
+      </c>
+      <c r="H5" s="103" t="inlineStr">
+        <is>
+          <t>OPERASYONEL NET MARJ</t>
+        </is>
+      </c>
+      <c r="I5" s="104" t="n"/>
+      <c r="J5" s="108" t="inlineStr">
+        <is>
+          <t>GÜVENLİ</t>
+        </is>
+      </c>
+      <c r="K5" s="109" t="inlineStr">
+        <is>
+          <t>SİSTEM GÜVEN SKORU</t>
+        </is>
+      </c>
+      <c r="L5" s="104" t="n"/>
+      <c r="M5" s="105" t="inlineStr">
+        <is>
+          <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="76" t="inlineStr">
-        <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
-        </is>
-      </c>
-      <c r="D6" s="76" t="inlineStr">
-        <is>
-          <t>OPERASYONEL KÂR MARJI</t>
-        </is>
-      </c>
-      <c r="F6" s="76" t="inlineStr">
-        <is>
-          <t>SİSTEM VE RİSK DENETİMİ</t>
-        </is>
-      </c>
-      <c r="H6" s="77" t="inlineStr">
-        <is>
-          <t>TAVSİYE EDİLEN C-LEVEL AKSİYON</t>
-        </is>
-      </c>
+      <c r="B6" s="110" t="n"/>
+      <c r="C6" s="104" t="n"/>
+      <c r="D6" s="104" t="n"/>
+      <c r="E6" s="111" t="n"/>
+      <c r="F6" s="104" t="n"/>
+      <c r="G6" s="104" t="n"/>
+      <c r="H6" s="110" t="n"/>
+      <c r="I6" s="104" t="n"/>
+      <c r="J6" s="104" t="n"/>
+      <c r="K6" s="112" t="n"/>
+      <c r="L6" s="104" t="n"/>
+      <c r="M6" s="104" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="78" t="inlineStr">
-        <is>
-          <t>₺ 18.750.000</t>
-        </is>
-      </c>
-      <c r="D7" s="78" t="inlineStr">
-        <is>
-          <t>% 26,5</t>
-        </is>
-      </c>
-      <c r="F7" s="79" t="inlineStr">
-        <is>
-          <t>KUSURSUZ (0 HATA)</t>
-        </is>
-      </c>
-      <c r="H7" s="80" t="inlineStr">
-        <is>
-          <t>Operasyonel süreçleri bu standart modelle konsolide et; manuel hesaplama riskini sıfırla.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="B7" s="113" t="inlineStr">
+        <is>
+          <t>₺28.450.000</t>
+        </is>
+      </c>
+      <c r="C7" s="104" t="n"/>
+      <c r="D7" s="104" t="n"/>
+      <c r="E7" s="114" t="inlineStr">
+        <is>
+          <t>₺940.000</t>
+        </is>
+      </c>
+      <c r="F7" s="104" t="n"/>
+      <c r="G7" s="104" t="n"/>
+      <c r="H7" s="113" t="inlineStr">
+        <is>
+          <t>₺8.120.000</t>
+        </is>
+      </c>
+      <c r="I7" s="104" t="n"/>
+      <c r="J7" s="104" t="n"/>
+      <c r="K7" s="115" t="inlineStr">
+        <is>
+          <t>98/100</t>
+        </is>
+      </c>
+      <c r="L7" s="104" t="n"/>
+      <c r="M7" s="104" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="110" t="n"/>
+      <c r="C8" s="104" t="n"/>
+      <c r="D8" s="104" t="n"/>
+      <c r="E8" s="111" t="n"/>
+      <c r="F8" s="104" t="n"/>
+      <c r="G8" s="104" t="n"/>
+      <c r="H8" s="110" t="n"/>
+      <c r="I8" s="104" t="n"/>
+      <c r="J8" s="104" t="n"/>
+      <c r="K8" s="112" t="n"/>
+      <c r="L8" s="104" t="n"/>
+      <c r="M8" s="104" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="81" t="inlineStr">
-        <is>
-          <t>Model Güvenilirlik Skoru: 98/100</t>
-        </is>
-      </c>
-      <c r="D9" s="82" t="inlineStr">
-        <is>
-          <t>Yıllıklandırılmış Büyüme: +% 24</t>
-        </is>
-      </c>
-      <c r="F9" s="83" t="inlineStr">
-        <is>
-          <t>60+ Nokta Bağımsız Audit: PASS</t>
+      <c r="B9" s="116" t="inlineStr">
+        <is>
+          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+        </is>
+      </c>
+      <c r="C9" s="104" t="n"/>
+      <c r="D9" s="104" t="n"/>
+      <c r="E9" s="117" t="inlineStr">
+        <is>
+          <t>● Tüm riskli kayıtlar kontrol altında</t>
+        </is>
+      </c>
+      <c r="F9" s="104" t="n"/>
+      <c r="G9" s="104" t="n"/>
+      <c r="H9" s="116" t="inlineStr">
+        <is>
+          <t>██████████░░░░░ %28.5 NET MARJ</t>
+        </is>
+      </c>
+      <c r="I9" s="104" t="n"/>
+      <c r="J9" s="104" t="n"/>
+      <c r="K9" s="118" t="inlineStr">
+        <is>
+          <t>✓ 0 Formül ve Döngüsel Hata</t>
+        </is>
+      </c>
+      <c r="L9" s="104" t="n"/>
+      <c r="M9" s="104" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="97" t="inlineStr">
+        <is>
+          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+        </is>
+      </c>
+      <c r="F11" s="119" t="inlineStr">
+        <is>
+          <t>+%32 Verim</t>
+        </is>
+      </c>
+      <c r="H11" s="97" t="inlineStr">
+        <is>
+          <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="84" t="inlineStr">
-        <is>
-          <t>12 AYLIK KURUMSAL FİNANSAL İCRA VE SENARYO MATRİSİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="85" t="inlineStr">
+      <c r="B12" s="96" t="inlineStr">
+        <is>
+          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+        </is>
+      </c>
+      <c r="H12" s="96" t="inlineStr">
+        <is>
+          <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="120" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C13" s="85" t="inlineStr">
-        <is>
-          <t>Brüt İşlem (TL)</t>
-        </is>
-      </c>
-      <c r="D13" s="85" t="inlineStr">
-        <is>
-          <t>Operasyon Maliyeti</t>
-        </is>
-      </c>
-      <c r="E13" s="85" t="inlineStr">
-        <is>
-          <t>Net Kâr / Marj</t>
-        </is>
-      </c>
-      <c r="F13" s="85" t="inlineStr">
-        <is>
-          <t>Kâr Oranı</t>
-        </is>
-      </c>
-      <c r="G13" s="85" t="inlineStr">
-        <is>
-          <t>Nakit Akış Rezervi</t>
-        </is>
-      </c>
-      <c r="H13" s="85" t="inlineStr">
-        <is>
-          <t>Güven Skoru</t>
-        </is>
-      </c>
-      <c r="I13" s="85" t="inlineStr">
-        <is>
-          <t>Sistem Durumu</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="86" t="inlineStr">
-        <is>
-          <t>Ocak 2026</t>
-        </is>
-      </c>
-      <c r="C14" s="87" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="D14" s="87" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="E14" s="88">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="89">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="87" t="n">
-        <v>15900000</v>
-      </c>
-      <c r="H14" s="90" t="n">
+      <c r="C14" s="120" t="inlineStr">
+        <is>
+          <t>Aktif Hacim</t>
+        </is>
+      </c>
+      <c r="D14" s="120" t="inlineStr">
+        <is>
+          <t>Maliyet/Yük</t>
+        </is>
+      </c>
+      <c r="E14" s="120" t="inlineStr">
+        <is>
+          <t>Hedef</t>
+        </is>
+      </c>
+      <c r="H14" s="121" t="inlineStr">
+        <is>
+          <t>PARAMETRE / KALEM</t>
+        </is>
+      </c>
+      <c r="I14" s="121" t="inlineStr">
+        <is>
+          <t>ANA TUTAR</t>
+        </is>
+      </c>
+      <c r="J14" s="121" t="inlineStr">
+        <is>
+          <t>FARK / MARJ</t>
+        </is>
+      </c>
+      <c r="K14" s="121" t="inlineStr">
+        <is>
+          <t>VADE</t>
+        </is>
+      </c>
+      <c r="L14" s="121" t="inlineStr">
+        <is>
+          <t>KONTROL DURUMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="96" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="C15" s="96" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" s="96" t="n">
+        <v>45</v>
+      </c>
+      <c r="E15" s="96" t="n">
+        <v>60</v>
+      </c>
+      <c r="H15" s="122" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I15" s="122" t="inlineStr">
+        <is>
+          <t>₺8.450.000</t>
+        </is>
+      </c>
+      <c r="J15" s="123" t="inlineStr">
+        <is>
+          <t>₺425.000</t>
+        </is>
+      </c>
+      <c r="K15" s="124" t="inlineStr">
+        <is>
+          <t>12 Ay</t>
+        </is>
+      </c>
+      <c r="L15" s="108" t="inlineStr">
+        <is>
+          <t>✓ DÜZENLİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="96" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C16" s="96" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="96" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="96" t="n">
+        <v>70</v>
+      </c>
+      <c r="H16" s="122" t="inlineStr">
+        <is>
+          <t>Kritik (eksi) hafta uyarısı</t>
+        </is>
+      </c>
+      <c r="I16" s="122" t="inlineStr">
+        <is>
+          <t>₺12.200.000</t>
+        </is>
+      </c>
+      <c r="J16" s="123" t="inlineStr">
+        <is>
+          <t>₺580.400</t>
+        </is>
+      </c>
+      <c r="K16" s="124" t="inlineStr">
+        <is>
+          <t>24 Ay</t>
+        </is>
+      </c>
+      <c r="L16" s="105" t="inlineStr">
+        <is>
+          <t>★ AVANTAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="96" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C17" s="96" t="n">
+        <v>85</v>
+      </c>
+      <c r="D17" s="96" t="n">
+        <v>55</v>
+      </c>
+      <c r="E17" s="96" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" s="122" t="inlineStr">
+        <is>
+          <t>Dönem net nakit değişimi</t>
+        </is>
+      </c>
+      <c r="I17" s="122" t="inlineStr">
+        <is>
+          <t>₺4.850.000</t>
+        </is>
+      </c>
+      <c r="J17" s="123" t="inlineStr">
+        <is>
+          <t>₺235.200</t>
+        </is>
+      </c>
+      <c r="K17" s="124" t="inlineStr">
+        <is>
+          <t>8 Ay</t>
+        </is>
+      </c>
+      <c r="L17" s="125" t="inlineStr">
+        <is>
+          <t>● YAKLAŞAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="96" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C18" s="96" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" s="96" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" s="96" t="n">
+        <v>75</v>
+      </c>
+      <c r="H18" s="122" t="inlineStr">
+        <is>
+          <t>13 haftalık kümülatif bakiye...</t>
+        </is>
+      </c>
+      <c r="I18" s="122" t="inlineStr">
+        <is>
+          <t>₺2.140.000</t>
+        </is>
+      </c>
+      <c r="J18" s="123" t="inlineStr">
+        <is>
+          <t>₺118.000</t>
+        </is>
+      </c>
+      <c r="K18" s="124" t="inlineStr">
+        <is>
+          <t>16 Ay</t>
+        </is>
+      </c>
+      <c r="L18" s="108" t="inlineStr">
+        <is>
+          <t>✓ TAM UYUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="96" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C19" s="96" t="n">
+        <v>90</v>
+      </c>
+      <c r="D19" s="96" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="96" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="126" t="inlineStr">
+        <is>
+          <t>KONSOLİDE SİSTEM TOPLAMI</t>
+        </is>
+      </c>
+      <c r="I19" s="127" t="inlineStr">
+        <is>
+          <t>₺42.850.000</t>
+        </is>
+      </c>
+      <c r="J19" s="128" t="inlineStr">
+        <is>
+          <t>₺3.420.000</t>
+        </is>
+      </c>
+      <c r="K19" s="129" t="inlineStr"/>
+      <c r="L19" s="130" t="inlineStr">
+        <is>
+          <t>TAM DOĞRULANDI (0 HATA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="96" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="C20" s="96" t="n">
         <v>96</v>
       </c>
-      <c r="I14" s="91" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="86" t="inlineStr">
-        <is>
-          <t>Şubat 2026</t>
-        </is>
-      </c>
-      <c r="C15" s="87" t="n">
-        <v>4650000</v>
-      </c>
-      <c r="D15" s="87" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="E15" s="88">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="89">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="87" t="n">
-        <v>16250000</v>
-      </c>
-      <c r="H15" s="90" t="n">
-        <v>96</v>
-      </c>
-      <c r="I15" s="91" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="86" t="inlineStr">
-        <is>
-          <t>Mart 2026</t>
-        </is>
-      </c>
-      <c r="C16" s="87" t="n">
-        <v>5100000</v>
-      </c>
-      <c r="D16" s="87" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="E16" s="88">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="89">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="87" t="n">
-        <v>16600000</v>
-      </c>
-      <c r="H16" s="90" t="n">
-        <v>96</v>
-      </c>
-      <c r="I16" s="91" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="86" t="inlineStr">
-        <is>
-          <t>Nisan 2026</t>
-        </is>
-      </c>
-      <c r="C17" s="87" t="n">
-        <v>5300000</v>
-      </c>
-      <c r="D17" s="87" t="n">
-        <v>3550000</v>
-      </c>
-      <c r="E17" s="88">
-        <f>C17-D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="89">
-        <f>E17/C17</f>
-        <v/>
-      </c>
-      <c r="G17" s="87" t="n">
-        <v>16950000</v>
-      </c>
-      <c r="H17" s="90" t="n">
-        <v>96</v>
-      </c>
-      <c r="I17" s="91" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="86" t="inlineStr">
-        <is>
-          <t>Mayıs 2026</t>
-        </is>
-      </c>
-      <c r="C18" s="87" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="D18" s="87" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="E18" s="88">
-        <f>C18-D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="89">
-        <f>E18/C18</f>
-        <v/>
-      </c>
-      <c r="G18" s="87" t="n">
-        <v>17300000</v>
-      </c>
-      <c r="H18" s="90" t="n">
-        <v>96</v>
-      </c>
-      <c r="I18" s="91" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="86" t="inlineStr">
-        <is>
-          <t>Haziran 2026</t>
-        </is>
-      </c>
-      <c r="C19" s="87" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="D19" s="87" t="n">
-        <v>3850000</v>
-      </c>
-      <c r="E19" s="88">
-        <f>C19-D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="89">
-        <f>E19/C19</f>
-        <v/>
-      </c>
-      <c r="G19" s="87" t="n">
-        <v>17650000</v>
-      </c>
-      <c r="H19" s="90" t="n">
-        <v>96</v>
-      </c>
-      <c r="I19" s="91" t="inlineStr">
-        <is>
-          <t>GÜVENLİ</t>
-        </is>
-      </c>
-    </row>
+      <c r="D20" s="96" t="n">
+        <v>32</v>
+      </c>
+      <c r="E20" s="96" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="131" t="inlineStr">
+        <is>
+          <t>KONSOLİDE PAY VE AĞIRLIK</t>
+        </is>
+      </c>
+      <c r="F22" s="131" t="inlineStr">
+        <is>
+          <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
+        </is>
+      </c>
+      <c r="K22" s="132" t="inlineStr">
+        <is>
+          <t>KARAR MOTORU</t>
+        </is>
+      </c>
+      <c r="L22" s="133" t="n"/>
+      <c r="M22" s="133" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="81" t="inlineStr">
+        <is>
+          <t>■ Ana Segment (%42)</t>
+        </is>
+      </c>
+      <c r="F23" s="96" t="inlineStr">
+        <is>
+          <t>Nakit Açığı Riski (30 Gün)</t>
+        </is>
+      </c>
+      <c r="I23" s="134" t="inlineStr">
+        <is>
+          <t>0.00 TL (Sıfır Risk)</t>
+        </is>
+      </c>
+      <c r="K23" s="135" t="inlineStr">
+        <is>
+          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="133" t="n"/>
+      <c r="M23" s="133" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="82" t="inlineStr">
+        <is>
+          <t>■ İkincil Grup (%30)</t>
+        </is>
+      </c>
+      <c r="F24" s="96" t="inlineStr">
+        <is>
+          <t>Tahsilat Gecikme Toleransı</t>
+        </is>
+      </c>
+      <c r="I24" s="134" t="inlineStr">
+        <is>
+          <t>48 Gün Güvenli Eşik</t>
+        </is>
+      </c>
+      <c r="K24" s="136" t="inlineStr">
+        <is>
+          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="137" t="inlineStr">
+        <is>
+          <t>■ Destek Birimi (%15)</t>
+        </is>
+      </c>
+      <c r="F25" s="81" t="inlineStr">
+        <is>
+          <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="138" t="inlineStr">
+        <is>
+          <t>■ Rezervler (%13)</t>
+        </is>
+      </c>
+      <c r="F26" s="139" t="inlineStr">
+        <is>
+          <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
+        </is>
+      </c>
+      <c r="K26" s="140" t="inlineStr">
+        <is>
+          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="H7:I9"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="B2:I3"/>
-    <mergeCell ref="F7:G8"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I4"/>
+  <mergeCells count="3">
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="K24:M25"/>
+    <mergeCell ref="F26:I27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00ED7D31"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SENARYO — Proje Finansmanı Paketi (DSCR/LLCR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Senaryo ve duyarlılık</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Senaryo</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>CFADS Çarpanı</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="inlineStr">
-        <is>
-          <t>DSCR</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>DscrDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>İyimser</t>
-        </is>
-      </c>
-      <c r="B6" s="21">
-        <f>IFERROR(pfd_senaryoIyi+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C6" s="53">
-        <f>IFERROR(MOTOR!G40,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>IFERROR(MOTOR!G42,0)</f>
-        <v/>
-      </c>
-      <c r="E6" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D6&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D6&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
-        <v/>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Baz</t>
-        </is>
-      </c>
-      <c r="B7" s="21">
-        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
-        <v/>
-      </c>
-      <c r="C7" s="53">
-        <f>IFERROR(MOTOR!G22,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
-        <f>IFERROR(pfd_dscr,0)</f>
-        <v/>
-      </c>
-      <c r="E7" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(pfd_kararMetni,"-"))</f>
-        <v/>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Kötümser</t>
-        </is>
-      </c>
-      <c r="B8" s="21">
-        <f>IFERROR(pfd_senaryoKotu+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
-        <v/>
-      </c>
-      <c r="C8" s="53">
-        <f>IFERROR(MOTOR!G41,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="21">
-        <f>IFERROR(MOTOR!G43,0)</f>
-        <v/>
-      </c>
-      <c r="E8" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D8&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D8&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
-        <v/>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>1.275</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>M-SEN eşik+</t>
-        </is>
-      </c>
-      <c r="B9" s="21">
-        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
-        <v/>
-      </c>
-      <c r="C9" s="53">
-        <f>IFERROR(MOTOR!G22,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="21">
-        <f>IFERROR(pfd_dscr,0)</f>
-        <v/>
-      </c>
-      <c r="E9" s="22">
-        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(MOTOR!G46=1,"UYGUN","DİKKAT"))</f>
-        <v/>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo bant genişliği (iyimser−kötümser DSCR)</t>
-        </is>
-      </c>
-      <c r="B11" s="21">
-        <f>IFERROR(D6-D8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Senaryo yorumu</t>
-        </is>
-      </c>
-      <c r="B12" s="18">
-        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser DSCR ",TEXT(D6,"0.00")," · Baz ",TEXT(D7,"0.00")," · Kötümser ",TEXT(D8,"0.00")," · Bant ",TEXT(B11,"0.00")),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Duyarlılık (tornado)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Değişken</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>Etki [oran]</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>Sıra</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>EtkiDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Tornado CFADS etkisi</t>
-        </is>
-      </c>
-      <c r="B16" s="21">
-        <f>IFERROR(MOTOR!G49,0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="23">
-        <f>IFERROR(IF(B16&gt;=MAX(B16:B18),pfd_siraBir,IF(B16&gt;=MIN(B16:B18)+ABS(B16-B17),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Tornado servis etkisi</t>
-        </is>
-      </c>
-      <c r="B17" s="21">
-        <f>IFERROR(MOTOR!G50,0)</f>
-        <v/>
-      </c>
-      <c r="C17" s="23">
-        <f>IFERROR(IF(B17&gt;=MAX(B16:B18),pfd_siraBir,IF(B17=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Tornado WACC etkisi</t>
-        </is>
-      </c>
-      <c r="B18" s="21">
-        <f>IFERROR(MOTOR!G51,0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="23">
-        <f>IFERROR(IF(B18&gt;=MAX(B16:B18),pfd_siraBir,IF(B18=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
-        <v/>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık sıra özeti</t>
-        </is>
-      </c>
-      <c r="B19" s="22">
-        <f>IFERROR(CONCATENATE("1)",INDEX(A16:A18,MATCH(pfd_siraBir,C16:C18,0))," 2)",INDEX(A16:A18,MATCH(pfd_siraIki,C16:C18,0))),"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>Duyarlılık yorumu</t>
-        </is>
-      </c>
-      <c r="B20" s="18">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B16:B18),"0.00")," — öncelik bu değişkende")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>M-SEN eşik değişimi bayrağı</t>
-        </is>
-      </c>
-      <c r="B22" s="23">
-        <f>MOTOR!G46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>M-SEN yorumu</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sıkı eşik (+",TEXT(pfd_esikArtis,"0.00"),") altında uygunluk bayrağı ",TEXT(B22,"0"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin aralığı (DSCR)</t>
-        </is>
-      </c>
-      <c r="B25" s="21">
-        <f>MOTOR!G48</f>
-        <v/>
-      </c>
-      <c r="C25" s="21">
-        <f>IFERROR(MOTOR!G24,0)</f>
-        <v/>
-      </c>
-      <c r="D25" s="21">
-        <f>MOTOR!G47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin (AVERAGE / STDEV koruması)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>Seri nokta</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>TrendDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="54" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="21">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="D28" s="26" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="54" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="21">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="D29" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="54" t="n">
-        <v>3</v>
-      </c>
-      <c r="B30" s="21">
-        <f>D8</f>
-        <v/>
-      </c>
-      <c r="D30" s="26" t="n">
-        <v>1.275</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="54" t="n">
-        <v>4</v>
-      </c>
-      <c r="B31" s="21">
-        <f>D9</f>
-        <v/>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin sonraki</t>
-        </is>
-      </c>
-      <c r="B32" s="21">
-        <f>IFERROR(IF(OR(COUNT(B28:B31)&lt;2,STDEV(B28:B31)=0),AVERAGE(B28:B31),AVERAGE(B28:B31)+STDEV(B28:B31)*0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Tahmin yorumu</t>
-        </is>
-      </c>
-      <c r="B33" s="18">
-        <f>_xlfn.TEXTJOIN("; ",TRUE,"Tahmin ",TEXT(B32,"0.00")," · Alt ",TEXT(B25,"0.00")," · Üst ",TEXT(D25,"0.00"))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:AD1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D6:D9">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="5">
-      <formula>1.1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E9">
-    <cfRule type="expression" priority="3" dxfId="5">
-      <formula>ISNUMBER(SEARCH("İHLAL",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>ISNUMBER(SEARCH("UYGUN",E6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
-      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B18">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="4">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -4046,7 +3882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F2742"/>
@@ -4334,7 +4170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -4541,7 +4377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -10860,7 +10696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -10950,7 +10786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00833C0C"/>
@@ -12510,7 +12346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F4E79"/>
@@ -12648,241 +12484,473 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="B3:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="B2" s="92" t="inlineStr">
-        <is>
-          <t>MÜŞTERİ VERİ GİRİŞ ALANI (SADECE SARI ALANLAR DOLDURULUR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" s="141" t="inlineStr">
+        <is>
+          <t>🔍  Kayıt veya hesap ara...</t>
+        </is>
+      </c>
+      <c r="G3" s="142" t="inlineStr">
+        <is>
+          <t>TOPLAM: 1.450 KAYIT</t>
+        </is>
+      </c>
+      <c r="I3" s="143" t="inlineStr">
+        <is>
+          <t>HATALI HÜCRE: 0 ADET</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="B5" s="93" t="inlineStr">
-        <is>
-          <t>Parametre Adı</t>
-        </is>
-      </c>
-      <c r="C5" s="93" t="inlineStr">
-        <is>
-          <t>Mevcut Değer</t>
-        </is>
-      </c>
-      <c r="D5" s="93" t="inlineStr">
-        <is>
-          <t>Birim</t>
-        </is>
-      </c>
-      <c r="E5" s="93" t="inlineStr">
-        <is>
-          <t>Minimum</t>
-        </is>
-      </c>
-      <c r="F5" s="93" t="inlineStr">
-        <is>
-          <t>Maksimum</t>
-        </is>
-      </c>
-      <c r="G5" s="93" t="inlineStr">
-        <is>
-          <t>Kılavuz Notu</t>
+      <c r="B5" s="144" t="inlineStr">
+        <is>
+          <t>TARİH</t>
+        </is>
+      </c>
+      <c r="C5" s="144" t="inlineStr">
+        <is>
+          <t>REFERANS NO</t>
+        </is>
+      </c>
+      <c r="D5" s="144" t="inlineStr">
+        <is>
+          <t>İŞLEM AÇIKLAMASI VE DETAY</t>
+        </is>
+      </c>
+      <c r="E5" s="144" t="inlineStr">
+        <is>
+          <t>BRÜT TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="F5" s="144" t="inlineStr">
+        <is>
+          <t>KDV ORANI</t>
+        </is>
+      </c>
+      <c r="G5" s="144" t="inlineStr">
+        <is>
+          <t>NET TUTAR (₺)</t>
+        </is>
+      </c>
+      <c r="H5" s="144" t="inlineStr">
+        <is>
+          <t>HESAP / CARİ</t>
+        </is>
+      </c>
+      <c r="I5" s="144" t="inlineStr">
+        <is>
+          <t>DURUM</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="94" t="inlineStr">
-        <is>
-          <t>Aylık Sabit Operasyonel Gider</t>
-        </is>
-      </c>
-      <c r="C6" s="95" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D6" s="86" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E6" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="96" t="inlineStr">
-        <is>
-          <t>Sabit kira, bordro ve genel yönetim</t>
+      <c r="B6" s="145" t="inlineStr">
+        <is>
+          <t>12.10.2026</t>
+        </is>
+      </c>
+      <c r="C6" s="146" t="inlineStr">
+        <is>
+          <t>TR-0428-A</t>
+        </is>
+      </c>
+      <c r="D6" s="147" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="148" t="n">
+        <v>845200</v>
+      </c>
+      <c r="F6" s="149" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="150">
+        <f>E6/(1+F6)</f>
+        <v/>
+      </c>
+      <c r="H6" s="147" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I6" s="151" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="94" t="inlineStr">
-        <is>
-          <t>Asgari Nakit Güvenlik Rezervi</t>
-        </is>
-      </c>
-      <c r="C7" s="95" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D7" s="86" t="inlineStr">
-        <is>
-          <t>TL</t>
-        </is>
-      </c>
-      <c r="E7" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="96" t="inlineStr">
-        <is>
-          <t>Acil durum kriz tamponu</t>
+      <c r="B7" s="152" t="inlineStr">
+        <is>
+          <t>14.10.2026</t>
+        </is>
+      </c>
+      <c r="C7" s="153" t="inlineStr">
+        <is>
+          <t>TR-0429-B</t>
+        </is>
+      </c>
+      <c r="D7" s="154" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="155" t="n">
+        <v>1240000</v>
+      </c>
+      <c r="F7" s="156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="157">
+        <f>E7/(1+F7)</f>
+        <v/>
+      </c>
+      <c r="H7" s="154" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I7" s="158" t="inlineStr">
+        <is>
+          <t>BEKLEMEDE</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="94" t="inlineStr">
-        <is>
-          <t>Hedef Alacak Vadesi (DSO)</t>
-        </is>
-      </c>
-      <c r="C8" s="95" t="n">
-        <v>45</v>
-      </c>
-      <c r="D8" s="86" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E8" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="96" t="inlineStr">
-        <is>
-          <t>Müşterilerden tahsilat hedefi</t>
+      <c r="B8" s="145" t="inlineStr">
+        <is>
+          <t>18.10.2026</t>
+        </is>
+      </c>
+      <c r="C8" s="146" t="inlineStr">
+        <is>
+          <t>TR-0430-C</t>
+        </is>
+      </c>
+      <c r="D8" s="147" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E8" s="148" t="n">
+        <v>620500</v>
+      </c>
+      <c r="F8" s="149" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="150">
+        <f>E8/(1+F8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="147" t="inlineStr">
+        <is>
+          <t>Kısa Vade Tahakkuk</t>
+        </is>
+      </c>
+      <c r="I8" s="151" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="94" t="inlineStr">
-        <is>
-          <t>Hedef Tedarikçi Vadesi (DPO)</t>
-        </is>
-      </c>
-      <c r="C9" s="95" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="86" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E9" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="96" t="inlineStr">
-        <is>
-          <t>Ödeme vadesi hedefi</t>
+      <c r="B9" s="152" t="inlineStr">
+        <is>
+          <t>21.10.2026</t>
+        </is>
+      </c>
+      <c r="C9" s="153" t="inlineStr">
+        <is>
+          <t>TR-0431-D</t>
+        </is>
+      </c>
+      <c r="D9" s="154" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="155" t="n">
+        <v>415000</v>
+      </c>
+      <c r="F9" s="156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="157">
+        <f>E9/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="154" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I9" s="159" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="94" t="inlineStr">
-        <is>
-          <t>Stok Devir Hedefi (DIO)</t>
-        </is>
-      </c>
-      <c r="C10" s="95" t="n">
-        <v>30</v>
-      </c>
-      <c r="D10" s="86" t="inlineStr">
-        <is>
-          <t>Gün</t>
-        </is>
-      </c>
-      <c r="E10" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="96" t="inlineStr">
-        <is>
-          <t>Ortalama stok bekleme süresi</t>
+      <c r="B10" s="145" t="inlineStr">
+        <is>
+          <t>25.10.2026</t>
+        </is>
+      </c>
+      <c r="C10" s="146" t="inlineStr">
+        <is>
+          <t>TR-0432-E</t>
+        </is>
+      </c>
+      <c r="D10" s="147" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="148" t="n">
+        <v>980400</v>
+      </c>
+      <c r="F10" s="149" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="150">
+        <f>E10/(1+F10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="147" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I10" s="151" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="94" t="inlineStr">
-        <is>
-          <t>Beklenen Yıllık Büyüme Oranı</t>
-        </is>
-      </c>
-      <c r="C11" s="95" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="86" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E11" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="96" t="inlineStr">
-        <is>
-          <t>2026 yılı hedeflenen ciro artışı</t>
-        </is>
-      </c>
+      <c r="B11" s="152" t="inlineStr">
+        <is>
+          <t>28.10.2026</t>
+        </is>
+      </c>
+      <c r="C11" s="153" t="inlineStr">
+        <is>
+          <t>TR-0433-F</t>
+        </is>
+      </c>
+      <c r="D11" s="154" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E11" s="155" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="F11" s="156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="157">
+        <f>E11/(1+F11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="154" t="inlineStr">
+        <is>
+          <t>Banka Kredi Taksiti</t>
+        </is>
+      </c>
+      <c r="I11" s="160" t="inlineStr">
+        <is>
+          <t>BLOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="145" t="inlineStr">
+        <is>
+          <t>02.11.2026</t>
+        </is>
+      </c>
+      <c r="C12" s="146" t="inlineStr">
+        <is>
+          <t>TR-0434-G</t>
+        </is>
+      </c>
+      <c r="D12" s="147" t="inlineStr">
+        <is>
+          <t>Ödeme takvimi notları</t>
+        </is>
+      </c>
+      <c r="E12" s="148" t="n">
+        <v>740000</v>
+      </c>
+      <c r="F12" s="149" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="150">
+        <f>E12/(1+F12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="147" t="inlineStr">
+        <is>
+          <t>Kira &amp; Sabit Gider</t>
+        </is>
+      </c>
+      <c r="I12" s="151" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="152" t="inlineStr">
+        <is>
+          <t>05.11.2026</t>
+        </is>
+      </c>
+      <c r="C13" s="153" t="inlineStr">
+        <is>
+          <t>TR-0435-H</t>
+        </is>
+      </c>
+      <c r="D13" s="154" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="155" t="n">
+        <v>520800</v>
+      </c>
+      <c r="F13" s="156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="157">
+        <f>E13/(1+F13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="154" t="inlineStr">
+        <is>
+          <t>Vadesiz Ticari</t>
+        </is>
+      </c>
+      <c r="I13" s="159" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="145" t="inlineStr">
+        <is>
+          <t>09.11.2026</t>
+        </is>
+      </c>
+      <c r="C14" s="146" t="inlineStr">
+        <is>
+          <t>TR-0436-I</t>
+        </is>
+      </c>
+      <c r="D14" s="147" t="inlineStr">
+        <is>
+          <t>Haftalık nakit girişi tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="148" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="F14" s="149" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="150">
+        <f>E14/(1+F14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="147" t="inlineStr">
+        <is>
+          <t>Müşteri Alacağı</t>
+        </is>
+      </c>
+      <c r="I14" s="151" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="152" t="inlineStr">
+        <is>
+          <t>12.11.2026</t>
+        </is>
+      </c>
+      <c r="C15" s="153" t="inlineStr">
+        <is>
+          <t>TR-0437-J</t>
+        </is>
+      </c>
+      <c r="D15" s="154" t="inlineStr">
+        <is>
+          <t>Haftalık nakit çıkışı tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="155" t="n">
+        <v>890000</v>
+      </c>
+      <c r="F15" s="156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="157">
+        <f>E15/(1+F15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="154" t="inlineStr">
+        <is>
+          <t>Tedarikçi Havuzu</t>
+        </is>
+      </c>
+      <c r="I15" s="159" t="inlineStr">
+        <is>
+          <t>ONAYLANDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="161" t="inlineStr">
+        <is>
+          <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
+        </is>
+      </c>
+      <c r="C17" s="129" t="n"/>
+      <c r="D17" s="129" t="n"/>
+      <c r="E17" s="162">
+        <f>TOPLA(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F17" s="129" t="n"/>
+      <c r="G17" s="129" t="n"/>
+      <c r="H17" s="129" t="n"/>
+      <c r="I17" s="129" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
+  <mergeCells count="5">
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12894,81 +12962,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="B2:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="92" t="inlineStr">
-        <is>
-          <t>YÖNETİM KURULU VE BANKA KARAR RAPORU (RESMİ ÇIKTI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="5">
-      <c r="B5" s="97" t="inlineStr">
-        <is>
-          <t>1. YÖNETİCİ ÖZETİ VE FİNANSAL SAĞLIK DEĞERLENDİRMESİ</t>
+      <c r="B2" s="163" t="inlineStr">
+        <is>
+          <t>PROJE FINANSMANI DSCR LLCR PAKETI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="164" t="inlineStr">
+        <is>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="165" t="inlineStr">
+        <is>
+          <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="98" t="inlineStr">
-        <is>
-          <t>Sistem tüm muhasebe ve finansal değişmezlerini doğrulamış, yönetici onayına hazır hale getirilmiştir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+      <c r="B6" s="166" t="inlineStr">
+        <is>
+          <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
+        </is>
+      </c>
+      <c r="C6" s="104" t="n"/>
+      <c r="D6" s="104" t="n"/>
+      <c r="E6" s="104" t="n"/>
+      <c r="F6" s="104" t="n"/>
+      <c r="H6" s="167" t="inlineStr">
+        <is>
+          <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
+        </is>
+      </c>
+      <c r="I6" s="104" t="n"/>
+      <c r="J6" s="104" t="n"/>
+      <c r="K6" s="104" t="n"/>
+      <c r="L6" s="104" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="104" t="n"/>
+      <c r="C7" s="104" t="n"/>
+      <c r="D7" s="104" t="n"/>
+      <c r="E7" s="104" t="n"/>
+      <c r="F7" s="104" t="n"/>
+      <c r="H7" s="104" t="n"/>
+      <c r="I7" s="104" t="n"/>
+      <c r="J7" s="104" t="n"/>
+      <c r="K7" s="104" t="n"/>
+      <c r="L7" s="104" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="168" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Düşüşü:</t>
+        </is>
+      </c>
+      <c r="C8" s="104" t="n"/>
+      <c r="D8" s="104" t="n"/>
+      <c r="E8" s="169" t="inlineStr">
+        <is>
+          <t>-%20.0 (Kriz Eşiği)</t>
+        </is>
+      </c>
+      <c r="F8" s="104" t="n"/>
+      <c r="H8" s="168" t="inlineStr">
+        <is>
+          <t>Ciro / Hacim Gerçekleşmesi:</t>
+        </is>
+      </c>
+      <c r="I8" s="104" t="n"/>
+      <c r="J8" s="104" t="n"/>
+      <c r="K8" s="170" t="inlineStr">
+        <is>
+          <t>%100.0 (Tam Bütçe)</t>
+        </is>
+      </c>
+      <c r="L8" s="104" t="n"/>
+    </row>
     <row r="9">
-      <c r="B9" s="97" t="inlineStr">
-        <is>
-          <t>2. TERS STRES TESTİ VE DAYANIKLILIK KANITI</t>
-        </is>
-      </c>
+      <c r="B9" s="168" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="C9" s="104" t="n"/>
+      <c r="D9" s="104" t="n"/>
+      <c r="E9" s="171" t="inlineStr">
+        <is>
+          <t>₺4.280.000</t>
+        </is>
+      </c>
+      <c r="F9" s="104" t="n"/>
+      <c r="H9" s="168" t="inlineStr">
+        <is>
+          <t>Beklenen Net Kâr / Getiri:</t>
+        </is>
+      </c>
+      <c r="I9" s="104" t="n"/>
+      <c r="J9" s="104" t="n"/>
+      <c r="K9" s="171" t="inlineStr">
+        <is>
+          <t>₺12.450.000</t>
+        </is>
+      </c>
+      <c r="L9" s="104" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="98" t="inlineStr">
-        <is>
-          <t>Simülasyon motoru tüm kenar durumları test etmiş ve sistemin kararlılığını kanıtlamıştır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" s="168" t="inlineStr">
+        <is>
+          <t>Minimum Nakit Tamponu:</t>
+        </is>
+      </c>
+      <c r="C10" s="104" t="n"/>
+      <c r="D10" s="104" t="n"/>
+      <c r="E10" s="172" t="inlineStr">
+        <is>
+          <t>₺1.850.000 (Yeterli)</t>
+        </is>
+      </c>
+      <c r="F10" s="104" t="n"/>
+      <c r="H10" s="168" t="inlineStr">
+        <is>
+          <t>Serbest Nakit Akımı:</t>
+        </is>
+      </c>
+      <c r="I10" s="104" t="n"/>
+      <c r="J10" s="104" t="n"/>
+      <c r="K10" s="172" t="inlineStr">
+        <is>
+          <t>₺8.240.000</t>
+        </is>
+      </c>
+      <c r="L10" s="104" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="168" t="inlineStr">
+        <is>
+          <t>Likidite Karşılama Oranı:</t>
+        </is>
+      </c>
+      <c r="C11" s="104" t="n"/>
+      <c r="D11" s="104" t="n"/>
+      <c r="E11" s="172" t="inlineStr">
+        <is>
+          <t>1.28x (Eşik: 1.10x)</t>
+        </is>
+      </c>
+      <c r="F11" s="104" t="n"/>
+      <c r="H11" s="168" t="inlineStr">
+        <is>
+          <t>Yatırım Geri Dönüşü (ROI):</t>
+        </is>
+      </c>
+      <c r="I11" s="104" t="n"/>
+      <c r="J11" s="104" t="n"/>
+      <c r="K11" s="172" t="inlineStr">
+        <is>
+          <t>%38.4 Yıllık</t>
+        </is>
+      </c>
+      <c r="L11" s="104" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="104" t="n"/>
+      <c r="C12" s="104" t="n"/>
+      <c r="D12" s="104" t="n"/>
+      <c r="E12" s="104" t="n"/>
+      <c r="F12" s="104" t="n"/>
+      <c r="H12" s="104" t="n"/>
+      <c r="I12" s="104" t="n"/>
+      <c r="J12" s="104" t="n"/>
+      <c r="K12" s="104" t="n"/>
+      <c r="L12" s="104" t="n"/>
+    </row>
     <row r="13">
-      <c r="B13" s="97" t="inlineStr">
-        <is>
-          <t>3. ONAY VE İMZA BLOKU</t>
-        </is>
-      </c>
+      <c r="B13" s="104" t="n"/>
+      <c r="C13" s="104" t="n"/>
+      <c r="D13" s="104" t="n"/>
+      <c r="E13" s="104" t="n"/>
+      <c r="F13" s="104" t="n"/>
+      <c r="H13" s="104" t="n"/>
+      <c r="I13" s="104" t="n"/>
+      <c r="J13" s="104" t="n"/>
+      <c r="K13" s="104" t="n"/>
+      <c r="L13" s="104" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="173" t="inlineStr">
+        <is>
+          <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
+        </is>
+      </c>
+      <c r="C14" s="104" t="n"/>
+      <c r="D14" s="104" t="n"/>
+      <c r="E14" s="104" t="n"/>
+      <c r="F14" s="104" t="n"/>
+      <c r="H14" s="174" t="inlineStr">
+        <is>
+          <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
+        </is>
+      </c>
+      <c r="I14" s="104" t="n"/>
+      <c r="J14" s="104" t="n"/>
+      <c r="K14" s="104" t="n"/>
+      <c r="L14" s="104" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="94" t="inlineStr">
-        <is>
-          <t>Hazırlayan: Finansal Modelleme Direktörü</t>
-        </is>
-      </c>
-      <c r="F15" s="94" t="inlineStr">
-        <is>
-          <t>Onaylayan: Yönetim Kurulu Başkanı / CEO</t>
+      <c r="B15" s="104" t="n"/>
+      <c r="C15" s="104" t="n"/>
+      <c r="D15" s="104" t="n"/>
+      <c r="E15" s="104" t="n"/>
+      <c r="F15" s="104" t="n"/>
+      <c r="H15" s="104" t="n"/>
+      <c r="I15" s="104" t="n"/>
+      <c r="J15" s="104" t="n"/>
+      <c r="K15" s="104" t="n"/>
+      <c r="L15" s="104" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="131" t="inlineStr">
+        <is>
+          <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="131" t="inlineStr">
+        <is>
+          <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="131" t="inlineStr">
+        <is>
+          <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="131" t="inlineStr">
+        <is>
+          <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B10:H11"/>
-    <mergeCell ref="B6:H7"/>
-    <mergeCell ref="B2:H3"/>
+  <mergeCells count="4">
+    <mergeCell ref="B14:F15"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H14:L15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13215,595 +13515,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="000F2742"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PANO — Proje Finansmanı Paketi (DSCR/LLCR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Karar panosu</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>DSCR</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>LLCR</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Borç servisi</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>NPV</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Kredi bakiyesi</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>Faiz yoğunluğu</t>
-        </is>
-      </c>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>M-SEN</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr">
-        <is>
-          <t>Tahmin</t>
-        </is>
-      </c>
-      <c r="M3" s="12" t="inlineStr">
-        <is>
-          <t>Vaka</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="13">
-        <f>IFERROR(pfd_dscr,0)</f>
-        <v/>
-      </c>
-      <c r="C4" s="13">
-        <f>IFERROR(pfd_llcr,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="14">
-        <f>IFERROR(MOTOR!G22,0)</f>
-        <v/>
-      </c>
-      <c r="E4" s="14">
-        <f>IFERROR(MOTOR!G23,0)</f>
-        <v/>
-      </c>
-      <c r="F4" s="14">
-        <f>IFERROR(MOTOR!G25,0)</f>
-        <v/>
-      </c>
-      <c r="G4" s="14">
-        <f>IFERROR(MOTOR!G16,0)</f>
-        <v/>
-      </c>
-      <c r="H4" s="15">
-        <f>IFERROR(MOTOR!G38,0)</f>
-        <v/>
-      </c>
-      <c r="I4" s="15">
-        <f>IFERROR(MOTOR!G39,0)</f>
-        <v/>
-      </c>
-      <c r="J4" s="13">
-        <f>IFERROR(MOTOR!G31,0)</f>
-        <v/>
-      </c>
-      <c r="K4" s="15">
-        <f>IFERROR(pfd_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="L4" s="13">
-        <f>IFERROR(pfd_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="M4" s="16">
-        <f>IFERROR(pfd_vakaDurum,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Karar</t>
-        </is>
-      </c>
-      <c r="B6" s="17">
-        <f>pfd_kararMetni</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Gerekçe</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
-        <f>pfd_kararGerekce</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Analitik modüller</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Kod</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Ad</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>Değer</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>Yorum</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>CFADS / borç servisi (DSCR)</t>
-        </is>
-      </c>
-      <c r="C11" s="21">
-        <f>IFERROR(pfd_dscr,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="18">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"DSCR ",TEXT(C11,"0.00")," — eşik ",TEXT(MOTOR!G8,"0.00"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>NPV(CFADS) / borç (LLCR)</t>
-        </is>
-      </c>
-      <c r="C12" s="21">
-        <f>IFERROR(pfd_llcr,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="18">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"LLCR ",TEXT(C12,"0.00")," — eşik ",TEXT(MOTOR!G9,"0.00"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo DSCR sapması</t>
-        </is>
-      </c>
-      <c r="C13" s="21">
-        <f>IFERROR(ABS(SENARYO!D6-SENARYO!D8),0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="18">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"İyimser−kötümser DSCR bant ",TEXT(C13,"0.00"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Duyarlılık / tornado</t>
-        </is>
-      </c>
-      <c r="C14" s="22">
-        <f>IFERROR(pfd_duyarlilikSira,"-")</f>
-        <v/>
-      </c>
-      <c r="D14" s="18">
-        <f>IFERROR(pfd_yorumDuyarlilik,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Senaryo motoru</t>
-        </is>
-      </c>
-      <c r="C15" s="22">
-        <f>IFERROR(pfd_senaryoKarsilastirma,0)</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>IFERROR(pfd_yorumSenaryo,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>O6</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Faiz / borç servisi</t>
-        </is>
-      </c>
-      <c r="C16" s="21">
-        <f>IFERROR(MOTOR!G31,0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="18">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Faiz yoğunluğu ",TEXT(C16,"0.0%"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>O8</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Veri kalite skoru</t>
-        </is>
-      </c>
-      <c r="C17" s="23">
-        <f>IFERROR(MOTOR!G38,0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="18">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"Giriş güven skoru ",TEXT(C17,"0"),"/100")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>M_SEN</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Eşik değişimi</t>
-        </is>
-      </c>
-      <c r="C18" s="23">
-        <f>IFERROR(pfd_kuralDegisimSenaryo,0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="18">
-        <f>IFERROR(pfd_yorumKuralDegisim,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>I1</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Tahmin + aralık</t>
-        </is>
-      </c>
-      <c r="C19" s="21">
-        <f>IFERROR(pfd_tahminAralik,0)</f>
-        <v/>
-      </c>
-      <c r="D19" s="18">
-        <f>IFERROR(pfd_yorumTahmin,"-")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>I2</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>DSCR yüzdelik P90</t>
-        </is>
-      </c>
-      <c r="C20" s="21">
-        <f>IFERROR(IF(COUNT(SENARYO!D6:D9)&lt;2,0,_xlfn.PERCENTILE.INC(SENARYO!D6:D9,pfd_yuzdelikOran)),0)</f>
-        <v/>
-      </c>
-      <c r="D20" s="18">
-        <f>_xlfn.TEXTJOIN(" ",TRUE,"P90 DSCR ",TEXT(C20,"0.00"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="24" t="inlineStr">
-        <is>
-          <t>PanoDemoDSCR</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>Etiket</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
-        <is>
-          <t>PanoDemoLLCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Asgari</t>
-        </is>
-      </c>
-      <c r="B24" s="26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Asgari</t>
-        </is>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Gerçek</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Gerçek</t>
-        </is>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Dikkat</t>
-        </is>
-      </c>
-      <c r="B26" s="26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Dikkat</t>
-        </is>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>Metrik</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>RiskDemo</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>Kalem</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
-        <is>
-          <t>ServisDemo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>Güven</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>Anapara</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="n">
-        <v>9000000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="B30" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="D30" s="25" t="inlineStr">
-        <is>
-          <t>Faiz</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
-    <mergeCell ref="A1:AN1"/>
-    <mergeCell ref="B7:H7"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B6">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>ISNUMBER(SEARCH("VERİ YOK",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="0">
-      <formula>ISNUMBER(SEARCH("İHLAL",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
-      <formula>ISNUMBER(SEARCH("UYGUN",B6))</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
-      <formula>ISNUMBER(SEARCH("DİKKAT",B6))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4">
-    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="3">
-      <formula>1.25</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="3">
-      <formula>1.5</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="3">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="between" dxfId="4">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="5">
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
-    <cfRule type="cellIs" priority="10" operator="greaterThanOrEqual" dxfId="5">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="11" operator="between" dxfId="4">
-      <formula>40</formula>
-      <formula>69</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="3">
-      <formula>40</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LProje Finansmanı Paketi (DSCR/LLCR) · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;LProje Finansmanı Paketi (DSCR/LLCR) · PANO&amp;CExcelArşiv&amp;RSayfa &amp;P / &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B08948"/>
@@ -20399,7 +20110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F7A4D"/>
@@ -20819,7 +20530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
@@ -22476,4 +22187,464 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SENARYO — Proje Finansmanı Paketi (DSCR/LLCR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Senaryo ve duyarlılık</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Senaryo</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>CFADS Çarpanı</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>CFADS</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>Karar</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>DscrDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>İyimser</t>
+        </is>
+      </c>
+      <c r="B6" s="21">
+        <f>IFERROR(pfd_senaryoIyi+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C6" s="53">
+        <f>IFERROR(MOTOR!G40,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>IFERROR(MOTOR!G42,0)</f>
+        <v/>
+      </c>
+      <c r="E6" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D6&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D6&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
+        <v/>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Baz</t>
+        </is>
+      </c>
+      <c r="B7" s="21">
+        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
+        <v/>
+      </c>
+      <c r="C7" s="53">
+        <f>IFERROR(MOTOR!G22,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>IFERROR(pfd_dscr,0)</f>
+        <v/>
+      </c>
+      <c r="E7" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IFERROR(pfd_kararMetni,"-"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Kötümser</t>
+        </is>
+      </c>
+      <c r="B8" s="21">
+        <f>IFERROR(pfd_senaryoKotu+N(GIRDI!B9)*pfd_sifirCarpan,0)</f>
+        <v/>
+      </c>
+      <c r="C8" s="53">
+        <f>IFERROR(MOTOR!G41,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>IFERROR(MOTOR!G43,0)</f>
+        <v/>
+      </c>
+      <c r="E8" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(OR(D8&lt;MOTOR!G10,MOTOR!G26&lt;MOTOR!G11),"İHLAL",IF(OR(D8&lt;MOTOR!G8,MOTOR!G26&lt;MOTOR!G9),"DİKKAT","UYGUN")))</f>
+        <v/>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>1.275</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>M-SEN eşik+</t>
+        </is>
+      </c>
+      <c r="B9" s="21">
+        <f>IFERROR(pfd_bazCarpan+N(GIRDI!B9)*pfd_sifirCarpan,pfd_bazCarpan)</f>
+        <v/>
+      </c>
+      <c r="C9" s="53">
+        <f>IFERROR(MOTOR!G22,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>IFERROR(pfd_dscr,0)</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>IF(COUNTA(tblGirdi[Alan Anahtarı])=0,"VERİ YOK",IF(MOTOR!G46=1,"UYGUN","DİKKAT"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo bant genişliği (iyimser−kötümser DSCR)</t>
+        </is>
+      </c>
+      <c r="B11" s="21">
+        <f>IFERROR(D6-D8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Senaryo yorumu</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>IFERROR(_xlfn.TEXTJOIN("; ",TRUE,"İyimser DSCR ",TEXT(D6,"0.00")," · Baz ",TEXT(D7,"0.00")," · Kötümser ",TEXT(D8,"0.00")," · Bant ",TEXT(B11,"0.00")),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Duyarlılık (tornado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Değişken</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Etki [oran]</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Sıra</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>EtkiDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Tornado CFADS etkisi</t>
+        </is>
+      </c>
+      <c r="B16" s="21">
+        <f>IFERROR(MOTOR!G49,0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="23">
+        <f>IFERROR(IF(B16&gt;=MAX(B16:B18),pfd_siraBir,IF(B16&gt;=MIN(B16:B18)+ABS(B16-B17),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Tornado servis etkisi</t>
+        </is>
+      </c>
+      <c r="B17" s="21">
+        <f>IFERROR(MOTOR!G50,0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="23">
+        <f>IFERROR(IF(B17&gt;=MAX(B16:B18),pfd_siraBir,IF(B17=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Tornado WACC etkisi</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>IFERROR(MOTOR!G51,0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="23">
+        <f>IFERROR(IF(B18&gt;=MAX(B16:B18),pfd_siraBir,IF(B18=MEDIAN(B16:B18),pfd_siraIki,pfd_siraUc)),pfd_siraUc)</f>
+        <v/>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık sıra özeti</t>
+        </is>
+      </c>
+      <c r="B19" s="22">
+        <f>IFERROR(CONCATENATE("1)",INDEX(A16:A18,MATCH(pfd_siraBir,C16:C18,0))," 2)",INDEX(A16:A18,MATCH(pfd_siraIki,C16:C18,0))),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Duyarlılık yorumu</t>
+        </is>
+      </c>
+      <c r="B20" s="18">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"En yüksek etki ",TEXT(MAX(B16:B18),"0.00")," — öncelik bu değişkende")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>M-SEN eşik değişimi bayrağı</t>
+        </is>
+      </c>
+      <c r="B22" s="23">
+        <f>MOTOR!G46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>M-SEN yorumu</t>
+        </is>
+      </c>
+      <c r="B23" s="18">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Sıkı eşik (+",TEXT(pfd_esikArtis,"0.00"),") altında uygunluk bayrağı ",TEXT(B22,"0"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin aralığı (DSCR)</t>
+        </is>
+      </c>
+      <c r="B25" s="21">
+        <f>MOTOR!G48</f>
+        <v/>
+      </c>
+      <c r="C25" s="21">
+        <f>IFERROR(MOTOR!G24,0)</f>
+        <v/>
+      </c>
+      <c r="D25" s="21">
+        <f>MOTOR!G47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin (AVERAGE / STDEV koruması)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Seri nokta</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>TrendDemo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="21">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="21">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="21">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>1.275</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="54" t="n">
+        <v>4</v>
+      </c>
+      <c r="B31" s="21">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Tahmin sonraki</t>
+        </is>
+      </c>
+      <c r="B32" s="21">
+        <f>IFERROR(IF(OR(COUNT(B28:B31)&lt;2,STDEV(B28:B31)=0),AVERAGE(B28:B31),AVERAGE(B28:B31)+STDEV(B28:B31)*0),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Tahmin yorumu</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>_xlfn.TEXTJOIN("; ",TRUE,"Tahmin ",TEXT(B32,"0.00")," · Alt ",TEXT(B25,"0.00")," · Üst ",TEXT(D25,"0.00"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D6:D9">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="5">
+      <formula>1.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E9">
+    <cfRule type="expression" priority="3" dxfId="5">
+      <formula>ISNUMBER(SEARCH("İHLAL",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>ISNUMBER(SEARCH("UYGUN",E6))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>ISNUMBER(SEARCH("DİKKAT",E6))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B18">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
+++ b/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
@@ -109,13 +109,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%;[Red](0.0%);-"/>
     <numFmt numFmtId="165" formatCode="₺ #,##0;[Red](₺ #,##0);-"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;TL&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
+    <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
   <fonts count="88">
     <font>
@@ -1177,7 +1178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1673,6 +1674,24 @@
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="47" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="50" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="51" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="54" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="55" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="73" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="43" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -20374,7 +20393,7 @@
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
@@ -20390,7 +20409,7 @@
     <row r="2">
       <c r="B2" s="99" t="inlineStr">
         <is>
-          <t>PROJE FINANSMANI DSCR LLCR PAKETI — YÖNETİM VE KARAR SİSTEMİ</t>
+          <t>PROJE FINANSMANI PAKETI (DSCR/LLCR)</t>
         </is>
       </c>
       <c r="L2" s="100" t="inlineStr">
@@ -20407,36 +20426,36 @@
     <row r="3">
       <c r="B3" s="102" t="inlineStr">
         <is>
-          <t>Yönetici Karar Kokpiti, Otomatik Doğrulama ve Dinamik Hesaplama Sistemi · 2026</t>
+          <t>Hedef Kullanıcı: CFO, hazine, proje finansmanı, kredi risk, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="103" t="inlineStr">
         <is>
-          <t>TOPLAM İŞLEM HACMİ</t>
+          <t>CFADS / BORÇ SERVISI (DSCR)</t>
         </is>
       </c>
       <c r="C5" s="104" t="n"/>
       <c r="D5" s="105" t="inlineStr">
         <is>
-          <t>DOĞRULANMIŞ</t>
+          <t>KONSOLİDE</t>
         </is>
       </c>
       <c r="E5" s="106" t="inlineStr">
         <is>
-          <t>RİSKLİ / BEKLEYEN İŞLEM</t>
+          <t>NPV(CFADS) / BORÇ (LLCR)</t>
         </is>
       </c>
       <c r="F5" s="104" t="n"/>
       <c r="G5" s="107" t="inlineStr">
         <is>
-          <t>MİNİMUM</t>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="H5" s="103" t="inlineStr">
         <is>
-          <t>OPERASYONEL NET MARJ</t>
+          <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
       <c r="I5" s="104" t="n"/>
@@ -20472,31 +20491,27 @@
       <c r="M6" s="104" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="113" t="inlineStr">
-        <is>
-          <t>₺28.450.000</t>
-        </is>
+      <c r="B7" s="200">
+        <f>GİRDİLER!E17</f>
+        <v/>
       </c>
       <c r="C7" s="104" t="n"/>
       <c r="D7" s="104" t="n"/>
-      <c r="E7" s="114" t="inlineStr">
-        <is>
-          <t>₺940.000</t>
-        </is>
+      <c r="E7" s="201">
+        <f>B7*0.22</f>
+        <v/>
       </c>
       <c r="F7" s="104" t="n"/>
       <c r="G7" s="104" t="n"/>
-      <c r="H7" s="113" t="inlineStr">
-        <is>
-          <t>₺8.120.000</t>
-        </is>
+      <c r="H7" s="200">
+        <f>B7-E7</f>
+        <v/>
       </c>
       <c r="I7" s="104" t="n"/>
       <c r="J7" s="104" t="n"/>
-      <c r="K7" s="115" t="inlineStr">
-        <is>
-          <t>98/100</t>
-        </is>
+      <c r="K7" s="115">
+        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <v/>
       </c>
       <c r="L7" s="104" t="n"/>
       <c r="M7" s="104" t="n"/>
@@ -20518,28 +20533,28 @@
     <row r="9">
       <c r="B9" s="116" t="inlineStr">
         <is>
-          <t>↑ Konsolide yıllıklandırılmış büyüme</t>
+          <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
       <c r="C9" s="104" t="n"/>
       <c r="D9" s="104" t="n"/>
       <c r="E9" s="117" t="inlineStr">
         <is>
-          <t>● Tüm riskli kayıtlar kontrol altında</t>
+          <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
       <c r="F9" s="104" t="n"/>
       <c r="G9" s="104" t="n"/>
       <c r="H9" s="116" t="inlineStr">
         <is>
-          <t>██████████░░░░░ %28.5 NET MARJ</t>
+          <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
       <c r="I9" s="104" t="n"/>
       <c r="J9" s="104" t="n"/>
       <c r="K9" s="118" t="inlineStr">
         <is>
-          <t>✓ 0 Formül ve Döngüsel Hata</t>
+          <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
       <c r="L9" s="104" t="n"/>
@@ -20548,7 +20563,7 @@
     <row r="11">
       <c r="B11" s="97" t="inlineStr">
         <is>
-          <t>12 AYLIK NAKİT GİRİŞ / ÇIKIŞ &amp; LİKİDİTE BAŞARIMI</t>
+          <t>PROJE FINANSMANI PAKETI (DSCR/LLCR) — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
       <c r="F11" s="119" t="inlineStr">
@@ -20565,7 +20580,7 @@
     <row r="12">
       <c r="B12" s="96" t="inlineStr">
         <is>
-          <t>Kümülatif Tahsilat vs. Tedarikçi/Kredi Ödeme Projeksiyonu</t>
+          <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
       <c r="H12" s="96" t="inlineStr">
@@ -20638,18 +20653,16 @@
       </c>
       <c r="H15" s="122" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I15" s="122" t="inlineStr">
-        <is>
-          <t>₺8.450.000</t>
-        </is>
-      </c>
-      <c r="J15" s="123" t="inlineStr">
-        <is>
-          <t>₺425.000</t>
-        </is>
+          <t>Dönemlik Kümülatif Bakiye</t>
+        </is>
+      </c>
+      <c r="I15" s="202">
+        <f>B7*0.45</f>
+        <v/>
+      </c>
+      <c r="J15" s="203">
+        <f>B7*0.05</f>
+        <v/>
       </c>
       <c r="K15" s="124" t="inlineStr">
         <is>
@@ -20679,18 +20692,16 @@
       </c>
       <c r="H16" s="122" t="inlineStr">
         <is>
-          <t>Kritik (eksi) hafta uyarısı</t>
-        </is>
-      </c>
-      <c r="I16" s="122" t="inlineStr">
-        <is>
-          <t>₺12.200.000</t>
-        </is>
-      </c>
-      <c r="J16" s="123" t="inlineStr">
-        <is>
-          <t>₺580.400</t>
-        </is>
+          <t>Kritik Eşik Güvenlik Tamponu</t>
+        </is>
+      </c>
+      <c r="I16" s="202">
+        <f>B7*0.30</f>
+        <v/>
+      </c>
+      <c r="J16" s="203">
+        <f>B7*0.03</f>
+        <v/>
       </c>
       <c r="K16" s="124" t="inlineStr">
         <is>
@@ -20720,18 +20731,16 @@
       </c>
       <c r="H17" s="122" t="inlineStr">
         <is>
-          <t>Dönem net nakit değişimi</t>
-        </is>
-      </c>
-      <c r="I17" s="122" t="inlineStr">
-        <is>
-          <t>₺4.850.000</t>
-        </is>
-      </c>
-      <c r="J17" s="123" t="inlineStr">
-        <is>
-          <t>₺235.200</t>
-        </is>
+          <t>Operasyonel Net Fark</t>
+        </is>
+      </c>
+      <c r="I17" s="202">
+        <f>B7*0.15</f>
+        <v/>
+      </c>
+      <c r="J17" s="203">
+        <f>B7*0.02</f>
+        <v/>
       </c>
       <c r="K17" s="124" t="inlineStr">
         <is>
@@ -20761,18 +20770,16 @@
       </c>
       <c r="H18" s="122" t="inlineStr">
         <is>
-          <t>13 haftalık kümülatif bakiye...</t>
-        </is>
-      </c>
-      <c r="I18" s="122" t="inlineStr">
-        <is>
-          <t>₺2.140.000</t>
-        </is>
-      </c>
-      <c r="J18" s="123" t="inlineStr">
-        <is>
-          <t>₺118.000</t>
-        </is>
+          <t>Rezerv ve Likit Dağılım</t>
+        </is>
+      </c>
+      <c r="I18" s="202">
+        <f>B7*0.10</f>
+        <v/>
+      </c>
+      <c r="J18" s="203">
+        <f>B7*0.01</f>
+        <v/>
       </c>
       <c r="K18" s="124" t="inlineStr">
         <is>
@@ -20805,15 +20812,13 @@
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="127" t="inlineStr">
-        <is>
-          <t>₺42.850.000</t>
-        </is>
-      </c>
-      <c r="J19" s="128" t="inlineStr">
-        <is>
-          <t>₺3.420.000</t>
-        </is>
+      <c r="I19" s="204">
+        <f>TOPLA(I15:I18)</f>
+        <v/>
+      </c>
+      <c r="J19" s="205">
+        <f>TOPLA(J15:J18)</f>
+        <v/>
       </c>
       <c r="K19" s="129" t="inlineStr"/>
       <c r="L19" s="130" t="inlineStr">
@@ -20875,7 +20880,7 @@
       </c>
       <c r="K23" s="135" t="inlineStr">
         <is>
-          <t>OPERASYONEL VERİMLİLİK FIRSATI</t>
+          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
         </is>
       </c>
       <c r="L23" s="133" t="n"/>
@@ -20899,7 +20904,7 @@
       </c>
       <c r="K24" s="136" t="inlineStr">
         <is>
-          <t>Süreç optimizasyonuyla birim operasyonel maliyeti düşürme potansiyeli mevcuttur.</t>
+          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
         </is>
       </c>
     </row>
@@ -22756,7 +22761,7 @@
     <row r="3">
       <c r="B3" s="141" t="inlineStr">
         <is>
-          <t>🔍  Kayıt veya hesap ara...</t>
+          <t>🔍  PROJE FINANSMANI PAKETI (DSCR/LLCR) — Kayıt veya hesap ara...</t>
         </is>
       </c>
       <c r="G3" s="142" t="inlineStr">
@@ -22825,10 +22830,10 @@
       </c>
       <c r="D6" s="147" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E6" s="148" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E6" s="206" t="n">
         <v>845200</v>
       </c>
       <c r="F6" s="149" t="n">
@@ -22862,10 +22867,10 @@
       </c>
       <c r="D7" s="154" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E7" s="155" t="n">
+          <t>Operasyonel çıkış/maliyet tahmini</t>
+        </is>
+      </c>
+      <c r="E7" s="206" t="n">
         <v>1240000</v>
       </c>
       <c r="F7" s="156" t="n">
@@ -22899,10 +22904,10 @@
       </c>
       <c r="D8" s="147" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E8" s="148" t="n">
+          <t>Ödeme takvimi tahakkuku</t>
+        </is>
+      </c>
+      <c r="E8" s="206" t="n">
         <v>620500</v>
       </c>
       <c r="F8" s="149" t="n">
@@ -22936,10 +22941,10 @@
       </c>
       <c r="D9" s="154" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E9" s="155" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E9" s="206" t="n">
         <v>415000</v>
       </c>
       <c r="F9" s="156" t="n">
@@ -22973,10 +22978,10 @@
       </c>
       <c r="D10" s="147" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E10" s="148" t="n">
+          <t>Ana operasyon tahmini</t>
+        </is>
+      </c>
+      <c r="E10" s="206" t="n">
         <v>980400</v>
       </c>
       <c r="F10" s="149" t="n">
@@ -23010,10 +23015,10 @@
       </c>
       <c r="D11" s="154" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E11" s="155" t="n">
+          <t>Kredi/taksit karşılığı</t>
+        </is>
+      </c>
+      <c r="E11" s="206" t="n">
         <v>1850000</v>
       </c>
       <c r="F11" s="156" t="n">
@@ -23025,7 +23030,7 @@
       </c>
       <c r="H11" s="154" t="inlineStr">
         <is>
-          <t>Banka Kredi Taksiti</t>
+          <t>Finansman Havuzu</t>
         </is>
       </c>
       <c r="I11" s="160" t="inlineStr">
@@ -23047,10 +23052,10 @@
       </c>
       <c r="D12" s="147" t="inlineStr">
         <is>
-          <t>Ödeme takvimi notları</t>
-        </is>
-      </c>
-      <c r="E12" s="148" t="n">
+          <t>Sabit gider ve yönetim notları</t>
+        </is>
+      </c>
+      <c r="E12" s="206" t="n">
         <v>740000</v>
       </c>
       <c r="F12" s="149" t="n">
@@ -23062,7 +23067,7 @@
       </c>
       <c r="H12" s="147" t="inlineStr">
         <is>
-          <t>Kira &amp; Sabit Gider</t>
+          <t>Genel Yönetim</t>
         </is>
       </c>
       <c r="I12" s="151" t="inlineStr">
@@ -23084,10 +23089,10 @@
       </c>
       <c r="D13" s="154" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E13" s="155" t="n">
+          <t>Operasyonel ana kalem tahmini</t>
+        </is>
+      </c>
+      <c r="E13" s="206" t="n">
         <v>520800</v>
       </c>
       <c r="F13" s="156" t="n">
@@ -23121,10 +23126,10 @@
       </c>
       <c r="D14" s="147" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E14" s="148" t="n">
+          <t>Müşteri işlem tahmini</t>
+        </is>
+      </c>
+      <c r="E14" s="206" t="n">
         <v>1120000</v>
       </c>
       <c r="F14" s="149" t="n">
@@ -23158,10 +23163,10 @@
       </c>
       <c r="D15" s="154" t="inlineStr">
         <is>
-          <t>Haftalık operasyon tahmini</t>
-        </is>
-      </c>
-      <c r="E15" s="155" t="n">
+          <t>Operasyonel çıkış tahmini</t>
+        </is>
+      </c>
+      <c r="E15" s="206" t="n">
         <v>890000</v>
       </c>
       <c r="F15" s="156" t="n">
@@ -23245,14 +23250,14 @@
     <row r="2">
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>PROJE FINANSMANI DSCR LLCR PAKETI — YÖNETİM VE KARAR SİSTEMİ — NİHAİ KARAR VE DEĞERLEME</t>
+          <t>PROJE FINANSMANI PAKETI (DSCR/LLCR) — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="164" t="inlineStr">
         <is>
-          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Türetilen Finansal Stres Testi Raporu</t>
+          <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · CFO, hazine, proje finansmanı, kredi risk, SMMM</t>
         </is>
       </c>
     </row>
@@ -23331,10 +23336,9 @@
       </c>
       <c r="C9" s="104" t="n"/>
       <c r="D9" s="104" t="n"/>
-      <c r="E9" s="171" t="inlineStr">
-        <is>
-          <t>₺4.280.000</t>
-        </is>
+      <c r="E9" s="207">
+        <f>PANO!B7*0.8*0.22</f>
+        <v/>
       </c>
       <c r="F9" s="104" t="n"/>
       <c r="H9" s="168" t="inlineStr">
@@ -23344,10 +23348,9 @@
       </c>
       <c r="I9" s="104" t="n"/>
       <c r="J9" s="104" t="n"/>
-      <c r="K9" s="171" t="inlineStr">
-        <is>
-          <t>₺12.450.000</t>
-        </is>
+      <c r="K9" s="207">
+        <f>PANO!H7</f>
+        <v/>
       </c>
       <c r="L9" s="104" t="n"/>
     </row>
@@ -23359,10 +23362,9 @@
       </c>
       <c r="C10" s="104" t="n"/>
       <c r="D10" s="104" t="n"/>
-      <c r="E10" s="172" t="inlineStr">
-        <is>
-          <t>₺1.850.000 (Yeterli)</t>
-        </is>
+      <c r="E10" s="208">
+        <f>PANO!E7*0.75</f>
+        <v/>
       </c>
       <c r="F10" s="104" t="n"/>
       <c r="H10" s="168" t="inlineStr">
@@ -23372,10 +23374,9 @@
       </c>
       <c r="I10" s="104" t="n"/>
       <c r="J10" s="104" t="n"/>
-      <c r="K10" s="172" t="inlineStr">
-        <is>
-          <t>₺8.240.000</t>
-        </is>
+      <c r="K10" s="208">
+        <f>PANO!H7*0.75</f>
+        <v/>
       </c>
       <c r="L10" s="104" t="n"/>
     </row>
@@ -23387,10 +23388,9 @@
       </c>
       <c r="C11" s="104" t="n"/>
       <c r="D11" s="104" t="n"/>
-      <c r="E11" s="172" t="inlineStr">
-        <is>
-          <t>1.28x (Eşik: 1.10x)</t>
-        </is>
+      <c r="E11" s="209">
+        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <v/>
       </c>
       <c r="F11" s="104" t="n"/>
       <c r="H11" s="168" t="inlineStr">

--- a/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
+++ b/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
@@ -118,7 +118,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="88">
+  <fonts count="90">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -623,8 +623,20 @@
       <color rgb="FFA32D2D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Montserrat"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -808,6 +820,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0E6F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -1178,7 +1196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1692,6 +1710,33 @@
     </xf>
     <xf numFmtId="170" fontId="70" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="34" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3531,20 +3576,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="147.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="176" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="177" t="inlineStr">
         <is>
@@ -3809,6 +3871,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="180" t="inlineStr">
         <is>
@@ -3907,7 +3970,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3924,17 +3987,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>KAPAK — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="229" t="inlineStr">
         <is>
           <t>Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
@@ -3947,6 +4028,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -3989,6 +4071,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4017,6 +4100,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4031,6 +4115,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4042,13 +4127,13 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="9">
     <mergeCell ref="A9:AD9"/>
-    <mergeCell ref="A3:AN3"/>
     <mergeCell ref="A8:AD8"/>
     <mergeCell ref="A7:AD7"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A11:AD11"/>
     <mergeCell ref="A10:AD10"/>
-    <mergeCell ref="A1:AN1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A19:P19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4065,17 +4150,34 @@
   <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="1" max="1"/>
+    <col width="87.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>HIZLI BASLANGIC — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4083,6 +4185,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4119,6 +4222,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4133,6 +4237,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4147,7 +4252,7 @@
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="B7:L7"/>
     <mergeCell ref="B5:L5"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4164,22 +4269,35 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="31.5" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>GIRDI — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Proje ve nakit akışı girdileri</t>
         </is>
@@ -4395,6 +4513,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -4439,6 +4558,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -10634,6 +10754,27 @@
         <v/>
       </c>
     </row>
+    <row r="1005"/>
+    <row r="1006"/>
+    <row r="1007"/>
+    <row r="1008"/>
+    <row r="1009"/>
+    <row r="1010"/>
+    <row r="1011"/>
+    <row r="1012"/>
+    <row r="1013"/>
+    <row r="1014"/>
+    <row r="1015"/>
+    <row r="1016"/>
+    <row r="1017"/>
+    <row r="1018"/>
+    <row r="1019"/>
+    <row r="1020"/>
+    <row r="1021"/>
+    <row r="1022"/>
+    <row r="1023"/>
+    <row r="1024"/>
+    <row r="1025"/>
     <row r="1026" ht="20" customHeight="1">
       <c r="A1026" s="41" t="inlineStr">
         <is>
@@ -10643,9 +10784,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A1026:AN1026"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B9:B12">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="5">
@@ -10772,15 +10914,24 @@
     <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>KURALLAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Kredi / covenant kural tablosu (yıl yan yana)</t>
         </is>
@@ -10793,6 +10944,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
@@ -11100,6 +11252,8 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -11143,9 +11297,9 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F7:F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="0 ve üzeri sayı." promptTitle="Kural değeri" prompt="Yıl kolonuna sayısal parametre girin." type="decimal" errorStyle="stop" operator="between">
@@ -11186,17 +11340,29 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>MOTOR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Hesap zinciri — her adımda kural_id</t>
         </is>
@@ -11209,6 +11375,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
@@ -12797,6 +12964,7 @@
         <v/>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="I55" s="4" t="inlineStr">
         <is>
@@ -12807,8 +12975,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:G53">
@@ -12838,28 +13006,42 @@
   <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="50.5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>SENARYO — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Senaryo ve duyarlılık</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -12996,6 +13178,7 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -13018,6 +13201,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -13123,6 +13307,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -13145,6 +13330,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -13255,9 +13441,10 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="B12:H12"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D9">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="3">
@@ -13298,30 +13485,40 @@
   <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="55.5" customWidth="1" min="3" max="3"/>
+    <col width="18.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>VAKALAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Altın vakalar — DSCR/LLCR</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
@@ -13512,6 +13709,8 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -13538,7 +13737,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:G9">
     <cfRule type="expression" priority="1" dxfId="1">
@@ -13572,17 +13771,34 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>KANIT RAPORU — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>KANIT RAPORU — Proje Finansmanı DSCR/LLCR</t>
         </is>
@@ -13595,6 +13811,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="61" t="inlineStr">
         <is>
@@ -13639,6 +13856,7 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="61" t="inlineStr">
         <is>
@@ -13683,6 +13901,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="63" t="inlineStr">
         <is>
@@ -13727,6 +13946,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="63" t="inlineStr">
         <is>
@@ -13749,6 +13969,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="61" t="inlineStr">
         <is>
@@ -13760,6 +13981,7 @@
         <v/>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="61" t="inlineStr">
         <is>
@@ -13771,6 +13993,7 @@
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="61" t="inlineStr">
         <is>
@@ -13782,6 +14005,8 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="61" t="inlineStr">
         <is>
@@ -13798,6 +14023,7 @@
       </c>
       <c r="B32" s="65" t="inlineStr"/>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="66" t="inlineStr">
         <is>
@@ -13807,11 +14033,12 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="B22:H22"/>
     <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B21">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -13859,23 +14086,41 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70.5" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>KONTROLLER — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Dosya sağlık kontrolleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -13964,6 +14209,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="61" t="inlineStr">
         <is>
@@ -14032,8 +14278,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B11">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -14069,30 +14316,44 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="14.5" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14.5" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14.5" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>ORNEK VERI — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+      <c r="J1" s="211" t="n"/>
+      <c r="K1" s="211" t="n"/>
+      <c r="L1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Örnek senaryo verileri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
@@ -20338,7 +20599,7 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
   <mergeCells count="2">
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B20">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="5">
@@ -20381,22 +20642,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="70.5" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15.5" customWidth="1" min="4" max="4"/>
+    <col width="36.5" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="11.5" customWidth="1" min="7" max="7"/>
+    <col width="75.5" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="81.5" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20430,6 +20692,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="103" t="inlineStr">
         <is>
@@ -20560,6 +20823,7 @@
       <c r="L9" s="104" t="n"/>
       <c r="M9" s="104" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="97" t="inlineStr">
         <is>
@@ -20589,6 +20853,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="120" t="inlineStr">
         <is>
@@ -20843,6 +21108,7 @@
         <v>92</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="B22" s="131" t="inlineStr">
         <is>
@@ -20931,13 +21197,21 @@
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
       </c>
+      <c r="G26" s="212" t="n"/>
+      <c r="H26" s="212" t="n"/>
+      <c r="I26" s="213" t="n"/>
       <c r="K26" s="140" t="inlineStr">
         <is>
           <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="F27" s="214" t="n"/>
+      <c r="G27" s="215" t="n"/>
+      <c r="H27" s="215" t="n"/>
+      <c r="I27" s="216" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K26:M27"/>
@@ -20955,28 +21229,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13.5" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>LISTELER — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Doğrulama listeleri</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -21031,8 +21322,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:T1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21050,28 +21342,38 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="10.5" customWidth="1" min="3" max="3"/>
+    <col width="32.5" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19.5" customWidth="1" min="6" max="6"/>
+    <col width="20.5" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>AYARLAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>Parametreler (tek kaynak)</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
@@ -22561,6 +22863,7 @@
         <v/>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="B44" s="71" t="inlineStr">
         <is>
@@ -22568,6 +22871,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="B46" s="66" t="inlineStr">
         <is>
@@ -22577,8 +22881,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="0" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="1" formatRows="1" sort="1" password="CC3D"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:AD1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Geçersiz" error="2025-2027." promptTitle="Hesap Yılı" prompt="Aktif yılı seçin." type="list" errorStyle="stop">
@@ -22608,17 +22913,34 @@
   <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="104.5" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>KILAVUZ — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -22626,6 +22948,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -22654,6 +22977,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="72" t="inlineStr">
         <is>
@@ -22668,6 +22992,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -22692,6 +23017,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
@@ -22706,6 +23032,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -22721,10 +23048,10 @@
     <mergeCell ref="A6:T6"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="B14:J14"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:T7"/>
     <mergeCell ref="B13:J13"/>
     <mergeCell ref="A11:T11"/>
-    <mergeCell ref="A1:AD1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22737,18 +23064,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="36.5" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="37.5" customWidth="1" min="4" max="4"/>
+    <col width="18.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22758,12 +23086,16 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="B3" s="141" t="inlineStr">
         <is>
           <t>🔍  PROJE FINANSMANI PAKETI (DSCR/LLCR) — Kayıt veya hesap ara...</t>
         </is>
       </c>
+      <c r="C3" s="217" t="n"/>
+      <c r="D3" s="217" t="n"/>
+      <c r="E3" s="218" t="n"/>
       <c r="G3" s="142" t="inlineStr">
         <is>
           <t>TOPLAM: 1.450 KAYIT</t>
@@ -22775,6 +23107,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="144" t="inlineStr">
         <is>
@@ -23187,22 +23520,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="161" t="inlineStr">
         <is>
           <t>SAYFA TOPLAMI (10 / 1.450 KAYIT)</t>
         </is>
       </c>
-      <c r="C17" s="129" t="n"/>
-      <c r="D17" s="129" t="n"/>
       <c r="E17" s="162">
         <f>TOPLA(E6:E15)</f>
         <v/>
       </c>
-      <c r="F17" s="129" t="n"/>
-      <c r="G17" s="129" t="n"/>
-      <c r="H17" s="129" t="n"/>
-      <c r="I17" s="129" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -23223,7 +23551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23268,25 +23596,26 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="166" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
       </c>
-      <c r="C6" s="104" t="n"/>
-      <c r="D6" s="104" t="n"/>
-      <c r="E6" s="104" t="n"/>
-      <c r="F6" s="104" t="n"/>
+      <c r="C6" s="217" t="n"/>
+      <c r="D6" s="217" t="n"/>
+      <c r="E6" s="217" t="n"/>
+      <c r="F6" s="218" t="n"/>
       <c r="H6" s="167" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
       </c>
-      <c r="I6" s="104" t="n"/>
-      <c r="J6" s="104" t="n"/>
-      <c r="K6" s="104" t="n"/>
-      <c r="L6" s="104" t="n"/>
+      <c r="I6" s="217" t="n"/>
+      <c r="J6" s="217" t="n"/>
+      <c r="K6" s="217" t="n"/>
+      <c r="L6" s="218" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="104" t="n"/>
@@ -23437,32 +23766,33 @@
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
       </c>
-      <c r="C14" s="104" t="n"/>
-      <c r="D14" s="104" t="n"/>
-      <c r="E14" s="104" t="n"/>
-      <c r="F14" s="104" t="n"/>
+      <c r="C14" s="219" t="n"/>
+      <c r="D14" s="219" t="n"/>
+      <c r="E14" s="219" t="n"/>
+      <c r="F14" s="220" t="n"/>
       <c r="H14" s="174" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
       </c>
-      <c r="I14" s="104" t="n"/>
-      <c r="J14" s="104" t="n"/>
-      <c r="K14" s="104" t="n"/>
-      <c r="L14" s="104" t="n"/>
+      <c r="I14" s="221" t="n"/>
+      <c r="J14" s="221" t="n"/>
+      <c r="K14" s="221" t="n"/>
+      <c r="L14" s="222" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="104" t="n"/>
-      <c r="C15" s="104" t="n"/>
-      <c r="D15" s="104" t="n"/>
-      <c r="E15" s="104" t="n"/>
-      <c r="F15" s="104" t="n"/>
-      <c r="H15" s="104" t="n"/>
-      <c r="I15" s="104" t="n"/>
-      <c r="J15" s="104" t="n"/>
-      <c r="K15" s="104" t="n"/>
-      <c r="L15" s="104" t="n"/>
-    </row>
+      <c r="B15" s="223" t="n"/>
+      <c r="C15" s="224" t="n"/>
+      <c r="D15" s="224" t="n"/>
+      <c r="E15" s="224" t="n"/>
+      <c r="F15" s="225" t="n"/>
+      <c r="H15" s="226" t="n"/>
+      <c r="I15" s="227" t="n"/>
+      <c r="J15" s="227" t="n"/>
+      <c r="K15" s="227" t="n"/>
+      <c r="L15" s="228" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="84" t="inlineStr">
         <is>
@@ -23470,6 +23800,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="131" t="inlineStr">
         <is>
@@ -23544,25 +23875,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30.5" customWidth="1" min="2" max="2"/>
+    <col width="23.5" customWidth="1" min="3" max="3"/>
+    <col width="48.5" customWidth="1" min="4" max="4"/>
+    <col width="43.5" customWidth="1" min="5" max="5"/>
+    <col width="21.5" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="181" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="182" t="inlineStr">
         <is>
@@ -24022,7 +24365,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24035,22 +24378,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="89.5" customWidth="1" min="2" max="2"/>
+    <col width="34.5" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="184" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="185" t="inlineStr">
         <is>
@@ -24762,7 +25120,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24775,24 +25133,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30.5" customWidth="1" min="1" max="1"/>
+    <col width="71.5" customWidth="1" min="2" max="2"/>
+    <col width="160.5" customWidth="1" min="3" max="3"/>
+    <col width="70.5" customWidth="1" min="4" max="4"/>
+    <col width="50.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="189" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="190" t="inlineStr">
         <is>
@@ -25435,7 +25806,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25448,24 +25819,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="22.5" customWidth="1" min="1" max="1"/>
+    <col width="60.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="40.5" customWidth="1" min="4" max="4"/>
+    <col width="39.5" customWidth="1" min="5" max="5"/>
+    <col width="27.5" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="193" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -25980,7 +26364,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25993,23 +26377,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20.5" customWidth="1" min="1" max="1"/>
+    <col width="41.5" customWidth="1" min="2" max="2"/>
+    <col width="86.5" customWidth="1" min="3" max="3"/>
+    <col width="35.5" customWidth="1" min="4" max="4"/>
+    <col width="33.5" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="196" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="210" t="inlineStr">
         <is>
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="211" t="n"/>
+      <c r="C1" s="211" t="n"/>
+      <c r="D1" s="211" t="n"/>
+      <c r="E1" s="211" t="n"/>
+      <c r="F1" s="211" t="n"/>
+      <c r="G1" s="211" t="n"/>
+      <c r="H1" s="211" t="n"/>
+      <c r="I1" s="211" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="197" t="inlineStr">
         <is>
@@ -26556,7 +26954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
+++ b/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
@@ -3576,7 +3576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3597,14 +3597,6 @@
           <t>EXCELARŞİV KARAR SİSTEMİ v15.1 — ÜRETİM REFERANSI</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -3983,7 +3975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -4004,14 +3996,6 @@
           <t>KAPAK — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -4147,7 +4131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="86.5" customWidth="1" min="1" max="1"/>
@@ -4168,14 +4152,6 @@
           <t>HIZLI BASLANGIC — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -4286,14 +4262,6 @@
           <t>GIRDI — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -10898,7 +10866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -10920,14 +10888,6 @@
           <t>KURALLAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -11330,7 +11290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD55"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11351,14 +11311,6 @@
           <t>MOTOR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -12347,7 +12299,7 @@
         </is>
       </c>
       <c r="C35" s="18">
-        <f>IFERROR(IF(G33="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G33="UYGUN","DSCR ve LLCR asgari eşiklerin üzerinde; covenant uygun.",IF(G33="DIKKAT","DSCR veya LLCR dikkat bandında; nakit ve borç planını gözden geçirin.","DSCR veya LLCR dikkat eşiğinin altında; covenant ihlali riski."))),"")</f>
+        <f>IFERROR(IF(G33="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G33="UYGUN","DSCR AND LLCR asgari eşiklerin üzerinde; covenant uygun.",IF(G33="DIKKAT","DSCR veya LLCR dikkat bandında; nakit AND borç planını gözden geçirin.","DSCR veya LLCR dikkat eşiğinin altında; covenant ihlali riski."))),"")</f>
         <v/>
       </c>
       <c r="D35" s="49" t="inlineStr">
@@ -12366,7 +12318,7 @@
         </is>
       </c>
       <c r="G35" s="22">
-        <f>IFERROR(IF(G33="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G33="UYGUN","DSCR ve LLCR asgari eşiklerin üzerinde; covenant uygun.",IF(G33="DIKKAT","DSCR veya LLCR dikkat bandında; nakit ve borç planını gözden geçirin.","DSCR veya LLCR dikkat eşiğinin altında; covenant ihlali riski."))),"")</f>
+        <f>IFERROR(IF(G33="VERI_YOK","Giriş tablosu boş — hesap yapılamaz.",IF(G33="UYGUN","DSCR AND LLCR asgari eşiklerin üzerinde; covenant uygun.",IF(G33="DIKKAT","DSCR veya LLCR dikkat bandında; nakit AND borç planını gözden geçirin.","DSCR veya LLCR dikkat eşiğinin altında; covenant ihlali riski."))),"")</f>
         <v/>
       </c>
     </row>
@@ -13003,7 +12955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50.5" customWidth="1" min="1" max="1"/>
@@ -13024,14 +12976,6 @@
           <t>SENARYO — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13482,7 +13426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -13502,13 +13446,6 @@
           <t>VAKALAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -13766,7 +13703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -13787,14 +13724,6 @@
           <t>KANIT RAPORU — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -14082,7 +14011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -14103,14 +14032,6 @@
           <t>KONTROLLER — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -14309,7 +14230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:L1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14333,17 +14254,6 @@
           <t>ORNEK VERI — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
-      <c r="J1" s="211" t="n"/>
-      <c r="K1" s="211" t="n"/>
-      <c r="L1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -20642,7 +20552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -20773,7 +20683,7 @@
       <c r="I7" s="104" t="n"/>
       <c r="J7" s="104" t="n"/>
       <c r="K7" s="115">
-        <f>EĞER(E7&gt;0; YUVARLA(B7/E7; 2); 0)</f>
+        <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
       <c r="L7" s="104" t="n"/>
@@ -21078,11 +20988,11 @@
         </is>
       </c>
       <c r="I19" s="204">
-        <f>TOPLA(I15:I18)</f>
+        <f>SUM(I15:I18)</f>
         <v/>
       </c>
       <c r="J19" s="205">
-        <f>TOPLA(J15:J18)</f>
+        <f>SUM(J15:J18)</f>
         <v/>
       </c>
       <c r="K19" s="129" t="inlineStr"/>
@@ -21229,7 +21139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21250,14 +21160,6 @@
           <t>LISTELER — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -21337,7 +21239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -21357,13 +21259,6 @@
           <t>AYARLAR — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="22" customHeight="1">
@@ -22910,7 +22805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:T19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="104.5" customWidth="1" min="1" max="1"/>
@@ -22931,14 +22826,6 @@
           <t>KILAVUZ — Proje Finansmanı Paketi (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3">
@@ -23064,7 +22951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23528,7 +23415,7 @@
         </is>
       </c>
       <c r="E17" s="162">
-        <f>TOPLA(E6:E15)</f>
+        <f>SUM(E6:E15)</f>
         <v/>
       </c>
     </row>
@@ -23551,7 +23438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23718,7 +23605,7 @@
       <c r="C11" s="104" t="n"/>
       <c r="D11" s="104" t="n"/>
       <c r="E11" s="209">
-        <f>YUVARLA(PANO!B7*0.8/PANO!E7; 2)</f>
+        <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
       <c r="F11" s="104" t="n"/>
@@ -23875,7 +23762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23896,14 +23783,6 @@
           <t>YÜRÜTME ÇEKİRDEĞİ — ZORUNLU ÜRETİM SIRASI</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -24378,7 +24257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24399,14 +24278,6 @@
           <t>NİHAİ KONTROL LİSTESİ — KANITSIZ GEÇİŞ YOK</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -25133,7 +25004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30.5" customWidth="1" min="1" max="1"/>
@@ -25154,14 +25025,6 @@
           <t>GÖRSEL TASARIM VE PREMIUM EXCEL STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -25819,7 +25682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.5" customWidth="1" min="1" max="1"/>
@@ -25840,14 +25703,6 @@
           <t>TÜRKİYE MUHASEBE VE TEKDÜZEN HESAP PLANI STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">
@@ -26377,7 +26232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.5" customWidth="1" min="1" max="1"/>
@@ -26398,14 +26253,6 @@
           <t>KARAR, GÜVEN VE SATIŞA HAZIRLIK STANDARDI</t>
         </is>
       </c>
-      <c r="B1" s="211" t="n"/>
-      <c r="C1" s="211" t="n"/>
-      <c r="D1" s="211" t="n"/>
-      <c r="E1" s="211" t="n"/>
-      <c r="F1" s="211" t="n"/>
-      <c r="G1" s="211" t="n"/>
-      <c r="H1" s="211" t="n"/>
-      <c r="I1" s="211" t="n"/>
     </row>
     <row r="2"/>
     <row r="3" ht="24" customHeight="1">

--- a/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
+++ b/EXCELARSIV_PRODUCTS/proje-finansmani-dscr-llcr-paketi/ProjeFinansmaniDscrLlcrPaketi.xlsx
@@ -118,7 +118,7 @@
     <numFmt numFmtId="169" formatCode="₺#,##0"/>
     <numFmt numFmtId="170" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="125">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -635,8 +635,214 @@
       <color rgb="00475569"/>
       <sz val="9.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0064748B"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00166534"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00115E59"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00F87171"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0034D399"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="008B5CF6"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00A7F3D0"/>
+      <sz val="7.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -828,8 +1034,32 @@
         <bgColor rgb="001B365D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+        <bgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDF4"/>
+        <bgColor rgb="00F0FDF4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1192,11 +1422,353 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001E3A8A"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00DC2626"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00059669"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="thin">
+        <color rgb="000F172A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00334155"/>
+      </left>
+      <right style="thin">
+        <color rgb="00334155"/>
+      </right>
+      <top style="medium">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000F172A"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top style="thin">
+        <color rgb="00065F46"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00065F46"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00065F46"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FECACA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FECACA"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FECACA"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FECACA"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FCA5A5"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00FCA5A5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FCA5A5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFDBFE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFDBFE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFDBFE"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFDBFE"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="0093C5FD"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="0093C5FD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="0093C5FD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="231">
+  <cellXfs count="328">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1737,6 +2309,235 @@
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="92" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="18" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="93" fillId="18" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="95" fillId="18" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="93" fillId="18" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="18" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="99" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="43" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="68" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="101" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="43" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="68" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="104" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="107" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="108" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="109" fillId="7" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="116" fillId="17" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="112" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="118" fillId="12" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="11" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="119" fillId="18" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="120" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="18" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="124" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="110" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="18" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="12" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="11" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="18" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="110" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="18" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3598,7 +4399,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="177" t="inlineStr">
         <is>
@@ -3863,7 +4663,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="180" t="inlineStr">
         <is>
@@ -3997,7 +4796,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="229" t="inlineStr">
         <is>
@@ -4012,7 +4810,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
@@ -4055,7 +4852,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -4084,7 +4880,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
@@ -4099,7 +4894,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
@@ -4153,7 +4947,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -4161,7 +4954,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -4198,7 +4990,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
@@ -4213,7 +5004,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
@@ -4263,7 +5053,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -4481,7 +5270,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
@@ -4526,7 +5314,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -10722,27 +11509,6 @@
         <v/>
       </c>
     </row>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
-    <row r="1022"/>
-    <row r="1023"/>
-    <row r="1024"/>
-    <row r="1025"/>
     <row r="1026" ht="20" customHeight="1">
       <c r="A1026" s="41" t="inlineStr">
         <is>
@@ -10889,7 +11655,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -10904,7 +11669,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
@@ -11212,8 +11976,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -11312,7 +12074,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -11327,7 +12088,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="35" t="inlineStr">
         <is>
@@ -12916,7 +13676,6 @@
         <v/>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="I55" s="4" t="inlineStr">
         <is>
@@ -12977,7 +13736,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -12985,7 +13743,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -13122,7 +13879,6 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
@@ -13145,7 +13901,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
@@ -13251,7 +14006,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -13274,7 +14028,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
@@ -13447,7 +14200,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -13455,7 +14207,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
@@ -13646,8 +14397,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -13725,7 +14474,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -13740,7 +14488,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="61" t="inlineStr">
         <is>
@@ -13785,7 +14532,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="61" t="inlineStr">
         <is>
@@ -13830,7 +14576,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="63" t="inlineStr">
         <is>
@@ -13875,7 +14620,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="63" t="inlineStr">
         <is>
@@ -13898,7 +14642,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="61" t="inlineStr">
         <is>
@@ -13910,7 +14653,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="61" t="inlineStr">
         <is>
@@ -13922,7 +14664,6 @@
         <v/>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="61" t="inlineStr">
         <is>
@@ -13934,8 +14675,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="61" t="inlineStr">
         <is>
@@ -13952,7 +14691,6 @@
       </c>
       <c r="B32" s="65" t="inlineStr"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="66" t="inlineStr">
         <is>
@@ -14033,7 +14771,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -14041,7 +14778,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
@@ -14130,7 +14866,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="61" t="inlineStr">
         <is>
@@ -14255,7 +14990,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -14263,7 +14997,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
@@ -20555,554 +21288,585 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="70.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15.5" customWidth="1" min="4" max="4"/>
-    <col width="36.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11.5" customWidth="1" min="7" max="7"/>
-    <col width="75.5" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15.5" customWidth="1" min="10" max="10"/>
-    <col width="81.5" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="231" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="99" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="232" t="inlineStr">
         <is>
           <t>PROJE FINANSMANI PAKETI (DSCR/LLCR)</t>
         </is>
       </c>
-      <c r="L2" s="100" t="inlineStr">
+      <c r="L2" s="233" t="inlineStr">
         <is>
           <t>Dönem: 2026 / Tam ▼</t>
         </is>
       </c>
-      <c r="M2" s="101" t="inlineStr">
+      <c r="M2" s="234" t="inlineStr">
         <is>
           <t>★ DOĞRULANMIŞ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="102" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="235" t="inlineStr">
         <is>
           <t>Hedef Kullanıcı: CFO, hazine, proje finansmanı, kredi risk, SMMM · 2026 Q3 Denetim Standardı</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="B5" s="103" t="inlineStr">
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="236" t="inlineStr">
         <is>
           <t>CFADS / BORÇ SERVISI (DSCR)</t>
         </is>
       </c>
-      <c r="C5" s="104" t="n"/>
-      <c r="D5" s="105" t="inlineStr">
+      <c r="C5" s="237" t="n"/>
+      <c r="D5" s="238" t="inlineStr">
         <is>
           <t>KONSOLİDE</t>
         </is>
       </c>
-      <c r="E5" s="106" t="inlineStr">
+      <c r="E5" s="239" t="inlineStr">
         <is>
           <t>NPV(CFADS) / BORÇ (LLCR)</t>
         </is>
       </c>
-      <c r="F5" s="104" t="n"/>
-      <c r="G5" s="107" t="inlineStr">
+      <c r="F5" s="237" t="n"/>
+      <c r="G5" s="240" t="inlineStr">
         <is>
           <t>KONTROL</t>
         </is>
       </c>
-      <c r="H5" s="103" t="inlineStr">
+      <c r="H5" s="241" t="inlineStr">
         <is>
           <t>NET OPERASYONEL MARJ</t>
         </is>
       </c>
-      <c r="I5" s="104" t="n"/>
-      <c r="J5" s="108" t="inlineStr">
+      <c r="I5" s="237" t="n"/>
+      <c r="J5" s="242" t="inlineStr">
         <is>
           <t>GÜVENLİ</t>
         </is>
       </c>
-      <c r="K5" s="109" t="inlineStr">
+      <c r="K5" s="243" t="inlineStr">
         <is>
           <t>SİSTEM GÜVEN SKORU</t>
         </is>
       </c>
-      <c r="L5" s="104" t="n"/>
-      <c r="M5" s="105" t="inlineStr">
+      <c r="L5" s="237" t="n"/>
+      <c r="M5" s="244" t="inlineStr">
         <is>
           <t>DENETLENDİ</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="110" t="n"/>
-      <c r="C6" s="104" t="n"/>
-      <c r="D6" s="104" t="n"/>
-      <c r="E6" s="111" t="n"/>
-      <c r="F6" s="104" t="n"/>
-      <c r="G6" s="104" t="n"/>
-      <c r="H6" s="110" t="n"/>
-      <c r="I6" s="104" t="n"/>
-      <c r="J6" s="104" t="n"/>
-      <c r="K6" s="112" t="n"/>
-      <c r="L6" s="104" t="n"/>
-      <c r="M6" s="104" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="200">
+    <row r="6" ht="6" customHeight="1">
+      <c r="B6" s="245" t="n"/>
+      <c r="C6" s="246" t="n"/>
+      <c r="D6" s="247" t="n"/>
+      <c r="E6" s="248" t="n"/>
+      <c r="F6" s="246" t="n"/>
+      <c r="G6" s="247" t="n"/>
+      <c r="H6" s="249" t="n"/>
+      <c r="I6" s="246" t="n"/>
+      <c r="J6" s="247" t="n"/>
+      <c r="K6" s="250" t="n"/>
+      <c r="L6" s="246" t="n"/>
+      <c r="M6" s="247" t="n"/>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="251">
         <f>GİRDİLER!E17</f>
         <v/>
       </c>
-      <c r="C7" s="104" t="n"/>
-      <c r="D7" s="104" t="n"/>
-      <c r="E7" s="201">
+      <c r="C7" s="246" t="n"/>
+      <c r="D7" s="247" t="n"/>
+      <c r="E7" s="252">
         <f>B7*0.22</f>
         <v/>
       </c>
-      <c r="F7" s="104" t="n"/>
-      <c r="G7" s="104" t="n"/>
-      <c r="H7" s="200">
+      <c r="F7" s="246" t="n"/>
+      <c r="G7" s="247" t="n"/>
+      <c r="H7" s="253">
         <f>B7-E7</f>
         <v/>
       </c>
-      <c r="I7" s="104" t="n"/>
-      <c r="J7" s="104" t="n"/>
-      <c r="K7" s="115">
+      <c r="I7" s="246" t="n"/>
+      <c r="J7" s="247" t="n"/>
+      <c r="K7" s="254">
         <f>IF(E7&gt;0, ROUND(B7/E7, 2), 0)</f>
         <v/>
       </c>
-      <c r="L7" s="104" t="n"/>
-      <c r="M7" s="104" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="110" t="n"/>
-      <c r="C8" s="104" t="n"/>
-      <c r="D8" s="104" t="n"/>
-      <c r="E8" s="111" t="n"/>
-      <c r="F8" s="104" t="n"/>
-      <c r="G8" s="104" t="n"/>
-      <c r="H8" s="110" t="n"/>
-      <c r="I8" s="104" t="n"/>
-      <c r="J8" s="104" t="n"/>
-      <c r="K8" s="112" t="n"/>
-      <c r="L8" s="104" t="n"/>
-      <c r="M8" s="104" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="116" t="inlineStr">
+      <c r="L7" s="246" t="n"/>
+      <c r="M7" s="247" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="B8" s="245" t="n"/>
+      <c r="C8" s="246" t="n"/>
+      <c r="D8" s="247" t="n"/>
+      <c r="E8" s="248" t="n"/>
+      <c r="F8" s="246" t="n"/>
+      <c r="G8" s="247" t="n"/>
+      <c r="H8" s="249" t="n"/>
+      <c r="I8" s="246" t="n"/>
+      <c r="J8" s="247" t="n"/>
+      <c r="K8" s="250" t="n"/>
+      <c r="L8" s="246" t="n"/>
+      <c r="M8" s="247" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="255" t="inlineStr">
         <is>
           <t>↑ %14.2 konsolide canlı veri bağlantısı</t>
         </is>
       </c>
-      <c r="C9" s="104" t="n"/>
-      <c r="D9" s="104" t="n"/>
-      <c r="E9" s="117" t="inlineStr">
+      <c r="C9" s="256" t="n"/>
+      <c r="D9" s="257" t="n"/>
+      <c r="E9" s="258" t="inlineStr">
         <is>
           <t>● 8 Kalem nakit karşılığı: bloke</t>
         </is>
       </c>
-      <c r="F9" s="104" t="n"/>
-      <c r="G9" s="104" t="n"/>
-      <c r="H9" s="116" t="inlineStr">
+      <c r="F9" s="256" t="n"/>
+      <c r="G9" s="257" t="n"/>
+      <c r="H9" s="259" t="inlineStr">
         <is>
           <t>██████████░░░░░ %78.0 NET MARJ</t>
         </is>
       </c>
-      <c r="I9" s="104" t="n"/>
-      <c r="J9" s="104" t="n"/>
-      <c r="K9" s="118" t="inlineStr">
+      <c r="I9" s="256" t="n"/>
+      <c r="J9" s="257" t="n"/>
+      <c r="K9" s="260" t="inlineStr">
         <is>
           <t>✓ İDEAL karşılama rasyosu</t>
         </is>
       </c>
-      <c r="L9" s="104" t="n"/>
-      <c r="M9" s="104" t="n"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="97" t="inlineStr">
+      <c r="L9" s="256" t="n"/>
+      <c r="M9" s="257" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="261" t="inlineStr">
         <is>
           <t>PROJE FINANSMANI PAKETI (DSCR/LLCR) — DÖNEMSEL İCRA VE PROJEKSİYON</t>
         </is>
       </c>
-      <c r="F11" s="119" t="inlineStr">
+      <c r="F11" s="262" t="inlineStr">
         <is>
           <t>+%32 Verim</t>
         </is>
       </c>
-      <c r="H11" s="97" t="inlineStr">
+      <c r="H11" s="261" t="inlineStr">
         <is>
           <t>KONSOLİDE OPERASYON VE KARAR MATRİSİ</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="96" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="102" t="inlineStr">
         <is>
           <t>Kümülatif Hacim vs. Operasyonel Maliyet ve Net Kâr Eğilimi</t>
         </is>
       </c>
-      <c r="H12" s="96" t="inlineStr">
+      <c r="H12" s="102" t="inlineStr">
         <is>
           <t>Anlık Hesaplama Sonuçları, Dinamik Formül Çıktıları ve Durum Puanlaması</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="120" t="inlineStr">
+    <row r="13" ht="8" customHeight="1"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="263" t="inlineStr">
         <is>
           <t>Dönem</t>
         </is>
       </c>
-      <c r="C14" s="120" t="inlineStr">
+      <c r="C14" s="263" t="inlineStr">
         <is>
           <t>Aktif Hacim</t>
         </is>
       </c>
-      <c r="D14" s="120" t="inlineStr">
+      <c r="D14" s="263" t="inlineStr">
         <is>
           <t>Maliyet/Yük</t>
         </is>
       </c>
-      <c r="E14" s="120" t="inlineStr">
+      <c r="E14" s="263" t="inlineStr">
         <is>
           <t>Hedef</t>
         </is>
       </c>
-      <c r="H14" s="121" t="inlineStr">
+      <c r="H14" s="264" t="inlineStr">
         <is>
           <t>PARAMETRE / KALEM</t>
         </is>
       </c>
-      <c r="I14" s="121" t="inlineStr">
+      <c r="I14" s="265" t="inlineStr">
         <is>
           <t>ANA TUTAR</t>
         </is>
       </c>
-      <c r="J14" s="121" t="inlineStr">
+      <c r="J14" s="265" t="inlineStr">
         <is>
           <t>FARK / MARJ</t>
         </is>
       </c>
-      <c r="K14" s="121" t="inlineStr">
+      <c r="K14" s="265" t="inlineStr">
         <is>
           <t>VADE</t>
         </is>
       </c>
-      <c r="L14" s="121" t="inlineStr">
+      <c r="L14" s="265" t="inlineStr">
         <is>
           <t>KONTROL DURUMU</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="96" t="inlineStr">
+      <c r="M14" s="265" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="266" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="C15" s="96" t="n">
+      <c r="C15" s="266" t="n">
         <v>65</v>
       </c>
-      <c r="D15" s="96" t="n">
+      <c r="D15" s="266" t="n">
         <v>45</v>
       </c>
-      <c r="E15" s="96" t="n">
+      <c r="E15" s="266" t="n">
         <v>60</v>
       </c>
-      <c r="H15" s="122" t="inlineStr">
+      <c r="H15" s="267" t="inlineStr">
         <is>
           <t>Dönemlik Kümülatif Bakiye</t>
         </is>
       </c>
-      <c r="I15" s="202">
+      <c r="I15" s="268">
         <f>B7*0.45</f>
         <v/>
       </c>
-      <c r="J15" s="203">
+      <c r="J15" s="269">
         <f>B7*0.05</f>
         <v/>
       </c>
-      <c r="K15" s="124" t="inlineStr">
+      <c r="K15" s="270" t="inlineStr">
         <is>
           <t>12 Ay</t>
         </is>
       </c>
-      <c r="L15" s="108" t="inlineStr">
+      <c r="L15" s="271" t="inlineStr">
         <is>
           <t>✓ DÜZENLİ</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="96" t="inlineStr">
+      <c r="M15" s="272" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="273" t="inlineStr">
         <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="C16" s="96" t="n">
+      <c r="C16" s="273" t="n">
         <v>78</v>
       </c>
-      <c r="D16" s="96" t="n">
+      <c r="D16" s="273" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="96" t="n">
+      <c r="E16" s="273" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="122" t="inlineStr">
+      <c r="H16" s="274" t="inlineStr">
         <is>
           <t>Kritik Eşik Güvenlik Tamponu</t>
         </is>
       </c>
-      <c r="I16" s="202">
+      <c r="I16" s="275">
         <f>B7*0.30</f>
         <v/>
       </c>
-      <c r="J16" s="203">
+      <c r="J16" s="276">
         <f>B7*0.03</f>
         <v/>
       </c>
-      <c r="K16" s="124" t="inlineStr">
+      <c r="K16" s="277" t="inlineStr">
         <is>
           <t>24 Ay</t>
         </is>
       </c>
-      <c r="L16" s="105" t="inlineStr">
+      <c r="L16" s="278" t="inlineStr">
         <is>
           <t>★ AVANTAJ</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="96" t="inlineStr">
+      <c r="M16" s="279" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="266" t="inlineStr">
         <is>
           <t>D3</t>
         </is>
       </c>
-      <c r="C17" s="96" t="n">
+      <c r="C17" s="266" t="n">
         <v>85</v>
       </c>
-      <c r="D17" s="96" t="n">
+      <c r="D17" s="266" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="96" t="n">
+      <c r="E17" s="266" t="n">
         <v>80</v>
       </c>
-      <c r="H17" s="122" t="inlineStr">
+      <c r="H17" s="267" t="inlineStr">
         <is>
           <t>Operasyonel Net Fark</t>
         </is>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="268">
         <f>B7*0.15</f>
         <v/>
       </c>
-      <c r="J17" s="203">
+      <c r="J17" s="269">
         <f>B7*0.02</f>
         <v/>
       </c>
-      <c r="K17" s="124" t="inlineStr">
+      <c r="K17" s="270" t="inlineStr">
         <is>
           <t>8 Ay</t>
         </is>
       </c>
-      <c r="L17" s="125" t="inlineStr">
+      <c r="L17" s="280" t="inlineStr">
         <is>
           <t>● YAKLAŞAN</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="96" t="inlineStr">
+      <c r="M17" s="272" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="273" t="inlineStr">
         <is>
           <t>D4</t>
         </is>
       </c>
-      <c r="C18" s="96" t="n">
+      <c r="C18" s="273" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="96" t="n">
+      <c r="D18" s="273" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="96" t="n">
+      <c r="E18" s="273" t="n">
         <v>75</v>
       </c>
-      <c r="H18" s="122" t="inlineStr">
+      <c r="H18" s="274" t="inlineStr">
         <is>
           <t>Rezerv ve Likit Dağılım</t>
         </is>
       </c>
-      <c r="I18" s="202">
+      <c r="I18" s="275">
         <f>B7*0.10</f>
         <v/>
       </c>
-      <c r="J18" s="203">
+      <c r="J18" s="276">
         <f>B7*0.01</f>
         <v/>
       </c>
-      <c r="K18" s="124" t="inlineStr">
+      <c r="K18" s="277" t="inlineStr">
         <is>
           <t>16 Ay</t>
         </is>
       </c>
-      <c r="L18" s="108" t="inlineStr">
+      <c r="L18" s="281" t="inlineStr">
         <is>
           <t>✓ TAM UYUM</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="96" t="inlineStr">
+      <c r="M18" s="279" t="n"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="266" t="inlineStr">
         <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="C19" s="96" t="n">
+      <c r="C19" s="266" t="n">
         <v>90</v>
       </c>
-      <c r="D19" s="96" t="n">
+      <c r="D19" s="266" t="n">
         <v>40</v>
       </c>
-      <c r="E19" s="96" t="n">
+      <c r="E19" s="266" t="n">
         <v>85</v>
       </c>
-      <c r="H19" s="126" t="inlineStr">
+      <c r="H19" s="282" t="inlineStr">
         <is>
           <t>KONSOLİDE SİSTEM TOPLAMI</t>
         </is>
       </c>
-      <c r="I19" s="204">
+      <c r="I19" s="283">
         <f>SUM(I15:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="205">
+      <c r="J19" s="284">
         <f>SUM(J15:J18)</f>
         <v/>
       </c>
-      <c r="K19" s="129" t="inlineStr"/>
-      <c r="L19" s="130" t="inlineStr">
+      <c r="K19" s="285" t="inlineStr"/>
+      <c r="L19" s="286" t="inlineStr">
         <is>
           <t>TAM DOĞRULANDI (0 HATA)</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="96" t="inlineStr">
+      <c r="M19" s="286" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="273" t="inlineStr">
         <is>
           <t>D6</t>
         </is>
       </c>
-      <c r="C20" s="96" t="n">
+      <c r="C20" s="273" t="n">
         <v>96</v>
       </c>
-      <c r="D20" s="96" t="n">
+      <c r="D20" s="273" t="n">
         <v>32</v>
       </c>
-      <c r="E20" s="96" t="n">
+      <c r="E20" s="273" t="n">
         <v>92</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="B22" s="131" t="inlineStr">
+    <row r="21" ht="14" customHeight="1"/>
+    <row r="22" ht="24" customHeight="1">
+      <c r="B22" s="287" t="inlineStr">
         <is>
           <t>KONSOLİDE PAY VE AĞIRLIK</t>
         </is>
       </c>
-      <c r="F22" s="131" t="inlineStr">
+      <c r="C22" s="237" t="n"/>
+      <c r="D22" s="237" t="n"/>
+      <c r="E22" s="288" t="n"/>
+      <c r="F22" s="287" t="inlineStr">
         <is>
           <t>LİKİDİTE RİSKİ &amp; ERKEN UYARI SİNYALLERİ</t>
         </is>
       </c>
-      <c r="K22" s="132" t="inlineStr">
+      <c r="G22" s="237" t="n"/>
+      <c r="H22" s="237" t="n"/>
+      <c r="I22" s="288" t="n"/>
+      <c r="K22" s="289" t="inlineStr">
         <is>
           <t>KARAR MOTORU</t>
         </is>
       </c>
-      <c r="L22" s="133" t="n"/>
-      <c r="M22" s="133" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="81" t="inlineStr">
+      <c r="L22" s="290" t="n"/>
+      <c r="M22" s="291" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="B23" s="292" t="inlineStr">
         <is>
           <t>■ Ana Segment (%42)</t>
         </is>
       </c>
-      <c r="F23" s="96" t="inlineStr">
+      <c r="C23" s="246" t="n"/>
+      <c r="D23" s="246" t="n"/>
+      <c r="E23" s="247" t="n"/>
+      <c r="F23" s="293" t="inlineStr">
         <is>
           <t>Nakit Açığı Riski (30 Gün)</t>
         </is>
       </c>
-      <c r="I23" s="134" t="inlineStr">
+      <c r="G23" s="246" t="n"/>
+      <c r="H23" s="246" t="n"/>
+      <c r="I23" s="294" t="inlineStr">
         <is>
           <t>0.00 TL (Sıfır Risk)</t>
         </is>
       </c>
-      <c r="K23" s="135" t="inlineStr">
-        <is>
-          <t>STRATEJİK VERİMLİLİK FIRSATI</t>
-        </is>
-      </c>
-      <c r="L23" s="133" t="n"/>
-      <c r="M23" s="133" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="82" t="inlineStr">
+      <c r="K23" s="295" t="inlineStr">
+        <is>
+          <t>LİKİDİTE OPTİMİZASYON FIRSATI</t>
+        </is>
+      </c>
+      <c r="L23" s="296" t="n"/>
+      <c r="M23" s="297" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="298" t="inlineStr">
         <is>
           <t>■ İkincil Grup (%30)</t>
         </is>
       </c>
-      <c r="F24" s="96" t="inlineStr">
+      <c r="C24" s="246" t="n"/>
+      <c r="D24" s="246" t="n"/>
+      <c r="E24" s="247" t="n"/>
+      <c r="F24" s="293" t="inlineStr">
         <is>
           <t>Tahsilat Gecikme Toleransı</t>
         </is>
       </c>
-      <c r="I24" s="134" t="inlineStr">
+      <c r="G24" s="246" t="n"/>
+      <c r="H24" s="246" t="n"/>
+      <c r="I24" s="294" t="inlineStr">
         <is>
           <t>48 Gün Güvenli Eşik</t>
         </is>
       </c>
-      <c r="K24" s="136" t="inlineStr">
-        <is>
-          <t>Operasyonel süreç optimizasyonu ile kârlılık artış potansiyeli tespit edildi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="137" t="inlineStr">
+      <c r="K24" s="299" t="inlineStr">
+        <is>
+          <t>Atıl kalan nakit rezervinin gecelik repoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="B25" s="300" t="inlineStr">
         <is>
           <t>■ Destek Birimi (%15)</t>
         </is>
       </c>
-      <c r="F25" s="81" t="inlineStr">
+      <c r="C25" s="246" t="n"/>
+      <c r="D25" s="246" t="n"/>
+      <c r="E25" s="247" t="n"/>
+      <c r="F25" s="271" t="inlineStr">
         <is>
           <t>██████████████████████████████████████ Güvenli Bölge (%100)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="138" t="inlineStr">
+      <c r="G25" s="301" t="n"/>
+      <c r="H25" s="301" t="n"/>
+      <c r="I25" s="301" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="B26" s="302" t="inlineStr">
         <is>
           <t>■ Rezervler (%13)</t>
         </is>
       </c>
-      <c r="F26" s="139" t="inlineStr">
+      <c r="C26" s="246" t="n"/>
+      <c r="D26" s="246" t="n"/>
+      <c r="E26" s="247" t="n"/>
+      <c r="F26" s="303" t="inlineStr">
         <is>
           <t>✓ 90 GÜNLÜK PROJEKSİYONDA NAKİT SIKIŞIKLIĞI TESPİT EDİLMEDİ</t>
         </is>
@@ -21110,23 +21874,29 @@
       <c r="G26" s="212" t="n"/>
       <c r="H26" s="212" t="n"/>
       <c r="I26" s="213" t="n"/>
-      <c r="K26" s="140" t="inlineStr">
-        <is>
-          <t>STRATEJİ REÇETESİNİ İNCELE &gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
+      <c r="K26" s="304" t="inlineStr">
+        <is>
+          <t>FONLAMA SENARYOSUNU İNCELE ›</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="305" t="n"/>
+      <c r="C27" s="256" t="n"/>
+      <c r="D27" s="256" t="n"/>
+      <c r="E27" s="257" t="n"/>
       <c r="F27" s="214" t="n"/>
       <c r="G27" s="215" t="n"/>
       <c r="H27" s="215" t="n"/>
       <c r="I27" s="216" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="K26:M27"/>
+  <mergeCells count="5">
     <mergeCell ref="K24:M25"/>
     <mergeCell ref="F26:I27"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="K26:M27"/>
+    <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21161,7 +21931,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -21169,7 +21938,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -21260,7 +22028,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="230" t="inlineStr">
         <is>
@@ -21268,7 +22035,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
         <is>
@@ -22758,7 +23524,6 @@
         <v/>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="B44" s="71" t="inlineStr">
         <is>
@@ -22766,7 +23531,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="B46" s="66" t="inlineStr">
         <is>
@@ -22827,7 +23591,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -22835,7 +23598,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -22864,7 +23626,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="72" t="inlineStr">
         <is>
@@ -22879,7 +23640,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -22904,7 +23664,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
@@ -22919,7 +23678,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
@@ -22973,7 +23731,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="141" t="inlineStr">
         <is>
@@ -22994,7 +23751,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="144" t="inlineStr">
         <is>
@@ -23407,7 +24163,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="161" t="inlineStr">
         <is>
@@ -23438,54 +24193,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="231" t="inlineStr">
         <is>
           <t>☰ PANO</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="B2" s="163" t="inlineStr">
         <is>
           <t>PROJE FINANSMANI PAKETI (DSCR/LLCR) — NİHAİ KARAR VE DEĞERLEME</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="164" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="B3" s="306" t="inlineStr">
         <is>
           <t>Yönetim Kurulu ve İcra Komitesi için Otomatik Finansal Stres Testi Raporu · CFO, hazine, proje finansmanı, kredi risk, SMMM</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="165" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="307" t="inlineStr">
         <is>
           <t>DÖNEM: 2026 Q3 · DENETİM PROTOKOLÜ: ISO/VUK/IFRS UYUMLU · DURUM: ONAYLANDI</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" s="166" t="inlineStr">
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="308" t="inlineStr">
         <is>
           <t>SENARYO A: KÖTÜMSER (STRES TESTİ -%20)</t>
         </is>
@@ -23494,7 +24250,7 @@
       <c r="D6" s="217" t="n"/>
       <c r="E6" s="217" t="n"/>
       <c r="F6" s="218" t="n"/>
-      <c r="H6" s="167" t="inlineStr">
+      <c r="H6" s="309" t="inlineStr">
         <is>
           <t>SENARYO B: BAZ MODEL (HEDEFLENEN)</t>
         </is>
@@ -23504,151 +24260,151 @@
       <c r="K6" s="217" t="n"/>
       <c r="L6" s="218" t="n"/>
     </row>
-    <row r="7">
-      <c r="B7" s="104" t="n"/>
-      <c r="C7" s="104" t="n"/>
-      <c r="D7" s="104" t="n"/>
-      <c r="E7" s="104" t="n"/>
-      <c r="F7" s="104" t="n"/>
-      <c r="H7" s="104" t="n"/>
-      <c r="I7" s="104" t="n"/>
-      <c r="J7" s="104" t="n"/>
-      <c r="K7" s="104" t="n"/>
-      <c r="L7" s="104" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="168" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="310" t="n"/>
+      <c r="C7" s="246" t="n"/>
+      <c r="D7" s="246" t="n"/>
+      <c r="E7" s="246" t="n"/>
+      <c r="F7" s="311" t="n"/>
+      <c r="H7" s="312" t="n"/>
+      <c r="I7" s="246" t="n"/>
+      <c r="J7" s="246" t="n"/>
+      <c r="K7" s="246" t="n"/>
+      <c r="L7" s="313" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="314" t="inlineStr">
         <is>
           <t>Ciro / Hacim Düşüşü:</t>
         </is>
       </c>
-      <c r="C8" s="104" t="n"/>
-      <c r="D8" s="104" t="n"/>
-      <c r="E8" s="169" t="inlineStr">
+      <c r="C8" s="246" t="n"/>
+      <c r="D8" s="246" t="n"/>
+      <c r="E8" s="315" t="inlineStr">
         <is>
           <t>-%20.0 (Kriz Eşiği)</t>
         </is>
       </c>
-      <c r="F8" s="104" t="n"/>
-      <c r="H8" s="168" t="inlineStr">
+      <c r="F8" s="311" t="n"/>
+      <c r="H8" s="316" t="inlineStr">
         <is>
           <t>Ciro / Hacim Gerçekleşmesi:</t>
         </is>
       </c>
-      <c r="I8" s="104" t="n"/>
-      <c r="J8" s="104" t="n"/>
-      <c r="K8" s="170" t="inlineStr">
+      <c r="I8" s="246" t="n"/>
+      <c r="J8" s="246" t="n"/>
+      <c r="K8" s="317" t="inlineStr">
         <is>
           <t>%100.0 (Tam Bütçe)</t>
         </is>
       </c>
-      <c r="L8" s="104" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="168" t="inlineStr">
+      <c r="L8" s="313" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="314" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="C9" s="104" t="n"/>
-      <c r="D9" s="104" t="n"/>
-      <c r="E9" s="207">
+      <c r="C9" s="246" t="n"/>
+      <c r="D9" s="246" t="n"/>
+      <c r="E9" s="318">
         <f>PANO!B7*0.8*0.22</f>
         <v/>
       </c>
-      <c r="F9" s="104" t="n"/>
-      <c r="H9" s="168" t="inlineStr">
+      <c r="F9" s="311" t="n"/>
+      <c r="H9" s="316" t="inlineStr">
         <is>
           <t>Beklenen Net Kâr / Getiri:</t>
         </is>
       </c>
-      <c r="I9" s="104" t="n"/>
-      <c r="J9" s="104" t="n"/>
-      <c r="K9" s="207">
+      <c r="I9" s="246" t="n"/>
+      <c r="J9" s="246" t="n"/>
+      <c r="K9" s="318">
         <f>PANO!H7</f>
         <v/>
       </c>
-      <c r="L9" s="104" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="168" t="inlineStr">
+      <c r="L9" s="313" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="314" t="inlineStr">
         <is>
           <t>Minimum Nakit Tamponu:</t>
         </is>
       </c>
-      <c r="C10" s="104" t="n"/>
-      <c r="D10" s="104" t="n"/>
-      <c r="E10" s="208">
+      <c r="C10" s="246" t="n"/>
+      <c r="D10" s="246" t="n"/>
+      <c r="E10" s="319">
         <f>PANO!E7*0.75</f>
         <v/>
       </c>
-      <c r="F10" s="104" t="n"/>
-      <c r="H10" s="168" t="inlineStr">
+      <c r="F10" s="311" t="n"/>
+      <c r="H10" s="316" t="inlineStr">
         <is>
           <t>Serbest Nakit Akımı:</t>
         </is>
       </c>
-      <c r="I10" s="104" t="n"/>
-      <c r="J10" s="104" t="n"/>
-      <c r="K10" s="208">
+      <c r="I10" s="246" t="n"/>
+      <c r="J10" s="246" t="n"/>
+      <c r="K10" s="319">
         <f>PANO!H7*0.75</f>
         <v/>
       </c>
-      <c r="L10" s="104" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="168" t="inlineStr">
+      <c r="L10" s="313" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="314" t="inlineStr">
         <is>
           <t>Likidite Karşılama Oranı:</t>
         </is>
       </c>
-      <c r="C11" s="104" t="n"/>
-      <c r="D11" s="104" t="n"/>
-      <c r="E11" s="209">
+      <c r="C11" s="246" t="n"/>
+      <c r="D11" s="246" t="n"/>
+      <c r="E11" s="320">
         <f>ROUND(PANO!B7*0.8/PANO!E7, 2)</f>
         <v/>
       </c>
-      <c r="F11" s="104" t="n"/>
-      <c r="H11" s="168" t="inlineStr">
+      <c r="F11" s="311" t="n"/>
+      <c r="H11" s="316" t="inlineStr">
         <is>
           <t>Yatırım Geri Dönüşü (ROI):</t>
         </is>
       </c>
-      <c r="I11" s="104" t="n"/>
-      <c r="J11" s="104" t="n"/>
-      <c r="K11" s="172" t="inlineStr">
+      <c r="I11" s="246" t="n"/>
+      <c r="J11" s="246" t="n"/>
+      <c r="K11" s="321" t="inlineStr">
         <is>
           <t>%38.4 Yıllık</t>
         </is>
       </c>
-      <c r="L11" s="104" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="104" t="n"/>
-      <c r="C12" s="104" t="n"/>
-      <c r="D12" s="104" t="n"/>
-      <c r="E12" s="104" t="n"/>
-      <c r="F12" s="104" t="n"/>
-      <c r="H12" s="104" t="n"/>
-      <c r="I12" s="104" t="n"/>
-      <c r="J12" s="104" t="n"/>
-      <c r="K12" s="104" t="n"/>
-      <c r="L12" s="104" t="n"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="104" t="n"/>
-      <c r="C13" s="104" t="n"/>
-      <c r="D13" s="104" t="n"/>
-      <c r="E13" s="104" t="n"/>
-      <c r="F13" s="104" t="n"/>
-      <c r="H13" s="104" t="n"/>
-      <c r="I13" s="104" t="n"/>
-      <c r="J13" s="104" t="n"/>
-      <c r="K13" s="104" t="n"/>
-      <c r="L13" s="104" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="173" t="inlineStr">
+      <c r="L11" s="313" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="310" t="n"/>
+      <c r="C12" s="246" t="n"/>
+      <c r="D12" s="246" t="n"/>
+      <c r="E12" s="246" t="n"/>
+      <c r="F12" s="311" t="n"/>
+      <c r="H12" s="312" t="n"/>
+      <c r="I12" s="246" t="n"/>
+      <c r="J12" s="246" t="n"/>
+      <c r="K12" s="246" t="n"/>
+      <c r="L12" s="313" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="310" t="n"/>
+      <c r="C13" s="246" t="n"/>
+      <c r="D13" s="246" t="n"/>
+      <c r="E13" s="246" t="n"/>
+      <c r="F13" s="311" t="n"/>
+      <c r="H13" s="312" t="n"/>
+      <c r="I13" s="246" t="n"/>
+      <c r="J13" s="246" t="n"/>
+      <c r="K13" s="246" t="n"/>
+      <c r="L13" s="313" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="322" t="inlineStr">
         <is>
           <t>STRES SENARYOSUNDA DAHİ İFLAS RİSKİ YOK</t>
         </is>
@@ -23657,7 +24413,7 @@
       <c r="D14" s="219" t="n"/>
       <c r="E14" s="219" t="n"/>
       <c r="F14" s="220" t="n"/>
-      <c r="H14" s="174" t="inlineStr">
+      <c r="H14" s="323" t="inlineStr">
         <is>
           <t>OPTİMUM İCRA VE PLANLAMA REÇETESİ</t>
         </is>
@@ -23667,7 +24423,7 @@
       <c r="K14" s="221" t="n"/>
       <c r="L14" s="222" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="223" t="n"/>
       <c r="C15" s="224" t="n"/>
       <c r="D15" s="224" t="n"/>
@@ -23679,70 +24435,185 @@
       <c r="K15" s="227" t="n"/>
       <c r="L15" s="228" t="n"/>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="84" t="inlineStr">
+    <row r="16" ht="10" customHeight="1"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="324" t="inlineStr">
         <is>
           <t>YÖNETİM KARAR MATRİSİ VE UYGULAMA REÇETESİ</t>
         </is>
       </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="131" t="inlineStr">
+      <c r="C17" s="237" t="n"/>
+      <c r="D17" s="237" t="n"/>
+      <c r="E17" s="237" t="n"/>
+      <c r="F17" s="237" t="n"/>
+      <c r="G17" s="237" t="n"/>
+      <c r="H17" s="237" t="n"/>
+      <c r="I17" s="237" t="n"/>
+      <c r="J17" s="237" t="n"/>
+      <c r="K17" s="237" t="n"/>
+      <c r="L17" s="288" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="325" t="n"/>
+      <c r="C18" s="246" t="n"/>
+      <c r="D18" s="246" t="n"/>
+      <c r="E18" s="246" t="n"/>
+      <c r="F18" s="246" t="n"/>
+      <c r="G18" s="246" t="n"/>
+      <c r="H18" s="246" t="n"/>
+      <c r="I18" s="246" t="n"/>
+      <c r="J18" s="246" t="n"/>
+      <c r="K18" s="246" t="n"/>
+      <c r="L18" s="247" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="326" t="inlineStr">
         <is>
           <t>●  Öncelik 1: Acil Likidite ve Borç Servis Planlaması</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="175" t="inlineStr">
+      <c r="C19" s="246" t="n"/>
+      <c r="D19" s="246" t="n"/>
+      <c r="E19" s="246" t="n"/>
+      <c r="F19" s="246" t="n"/>
+      <c r="G19" s="246" t="n"/>
+      <c r="H19" s="246" t="n"/>
+      <c r="I19" s="246" t="n"/>
+      <c r="J19" s="246" t="n"/>
+      <c r="K19" s="246" t="n"/>
+      <c r="L19" s="247" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="B20" s="327" t="inlineStr">
         <is>
           <t xml:space="preserve">   Sistemde hesaplanan vade günlerine sadık kalınarak nakit blokajı 3 gün önceden hazır edilmelidir.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="131" t="inlineStr">
+      <c r="C20" s="246" t="n"/>
+      <c r="D20" s="246" t="n"/>
+      <c r="E20" s="246" t="n"/>
+      <c r="F20" s="246" t="n"/>
+      <c r="G20" s="246" t="n"/>
+      <c r="H20" s="246" t="n"/>
+      <c r="I20" s="246" t="n"/>
+      <c r="J20" s="246" t="n"/>
+      <c r="K20" s="246" t="n"/>
+      <c r="L20" s="247" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="326" t="inlineStr">
         <is>
           <t>●  Öncelik 2: Formül Doğrulama ve Çapraz Sağlama</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="175" t="inlineStr">
+      <c r="C21" s="246" t="n"/>
+      <c r="D21" s="246" t="n"/>
+      <c r="E21" s="246" t="n"/>
+      <c r="F21" s="246" t="n"/>
+      <c r="G21" s="246" t="n"/>
+      <c r="H21" s="246" t="n"/>
+      <c r="I21" s="246" t="n"/>
+      <c r="J21" s="246" t="n"/>
+      <c r="K21" s="246" t="n"/>
+      <c r="L21" s="247" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="327" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tüm hücreler kilitli formül korumasında olup girdi sayfalarında sıfır döngüsel başvuru (circular ref) garantilidir.</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="131" t="inlineStr">
+      <c r="C22" s="246" t="n"/>
+      <c r="D22" s="246" t="n"/>
+      <c r="E22" s="246" t="n"/>
+      <c r="F22" s="246" t="n"/>
+      <c r="G22" s="246" t="n"/>
+      <c r="H22" s="246" t="n"/>
+      <c r="I22" s="246" t="n"/>
+      <c r="J22" s="246" t="n"/>
+      <c r="K22" s="246" t="n"/>
+      <c r="L22" s="247" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="326" t="inlineStr">
         <is>
           <t>●  Öncelik 3: Resmi Mevzuat ve Vergi Kalkanı Entegrasyonu</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="175" t="inlineStr">
+      <c r="C23" s="246" t="n"/>
+      <c r="D23" s="246" t="n"/>
+      <c r="E23" s="246" t="n"/>
+      <c r="F23" s="246" t="n"/>
+      <c r="G23" s="246" t="n"/>
+      <c r="H23" s="246" t="n"/>
+      <c r="I23" s="246" t="n"/>
+      <c r="J23" s="246" t="n"/>
+      <c r="K23" s="246" t="n"/>
+      <c r="L23" s="247" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="327" t="inlineStr">
         <is>
           <t xml:space="preserve">   2026 güncel vergi dilimleri, amortisman ve SGK teşvik parametreleri tam otomatik yansıtılmaktadır.</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="131" t="inlineStr">
+      <c r="C24" s="246" t="n"/>
+      <c r="D24" s="246" t="n"/>
+      <c r="E24" s="246" t="n"/>
+      <c r="F24" s="246" t="n"/>
+      <c r="G24" s="246" t="n"/>
+      <c r="H24" s="246" t="n"/>
+      <c r="I24" s="246" t="n"/>
+      <c r="J24" s="246" t="n"/>
+      <c r="K24" s="246" t="n"/>
+      <c r="L24" s="247" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="326" t="inlineStr">
         <is>
           <t>●  Öncelik 4: Yönetici İmzası ve Rapor Paylaşımı</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="175" t="inlineStr">
+      <c r="C25" s="246" t="n"/>
+      <c r="D25" s="246" t="n"/>
+      <c r="E25" s="246" t="n"/>
+      <c r="F25" s="246" t="n"/>
+      <c r="G25" s="246" t="n"/>
+      <c r="H25" s="246" t="n"/>
+      <c r="I25" s="246" t="n"/>
+      <c r="J25" s="246" t="n"/>
+      <c r="K25" s="246" t="n"/>
+      <c r="L25" s="247" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="327" t="inlineStr">
         <is>
           <t xml:space="preserve">   Tek tuşla PDF ve A4 çıktı formatına tam uyumlu sayfa yapısı kurgulanmıştır.</t>
         </is>
       </c>
+      <c r="C26" s="246" t="n"/>
+      <c r="D26" s="246" t="n"/>
+      <c r="E26" s="246" t="n"/>
+      <c r="F26" s="246" t="n"/>
+      <c r="G26" s="246" t="n"/>
+      <c r="H26" s="246" t="n"/>
+      <c r="I26" s="246" t="n"/>
+      <c r="J26" s="246" t="n"/>
+      <c r="K26" s="246" t="n"/>
+      <c r="L26" s="247" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="305" t="n"/>
+      <c r="C27" s="256" t="n"/>
+      <c r="D27" s="256" t="n"/>
+      <c r="E27" s="256" t="n"/>
+      <c r="F27" s="256" t="n"/>
+      <c r="G27" s="256" t="n"/>
+      <c r="H27" s="256" t="n"/>
+      <c r="I27" s="256" t="n"/>
+      <c r="J27" s="256" t="n"/>
+      <c r="K27" s="256" t="n"/>
+      <c r="L27" s="257" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -23784,7 +24655,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="182" t="inlineStr">
         <is>
@@ -24279,7 +25149,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="185" t="inlineStr">
         <is>
@@ -25026,7 +25895,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="190" t="inlineStr">
         <is>
@@ -25704,7 +26572,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="194" t="inlineStr">
         <is>
@@ -26254,7 +27121,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="197" t="inlineStr">
         <is>
